--- a/AAII_Financials/Quarterly/MRCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MRCY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,412 +656,424 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45289</v>
+      </c>
+      <c r="E7" s="2">
         <v>45198</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44925</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44743</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44652</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44470</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44379</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44288</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44197</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44106</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44015</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43917</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43826</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43735</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>197500</v>
+      </c>
+      <c r="E8" s="3">
         <v>181000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>253200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>263500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>229600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>227600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>289700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>253100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>220400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>225000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>250800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>256900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>210700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>205600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>217400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>208000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>193900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>177300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>177000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>174600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>159100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>144100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>152900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>116300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>117900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>106100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>115600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>107300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>98000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>87600</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>165900</v>
+      </c>
+      <c r="E9" s="3">
         <v>130500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>185900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>173200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>148600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>149500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>170200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>153300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>133200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>136600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>148100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>151200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>122000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>117500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>120800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>114700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>105400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>98900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>97100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>100800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>88200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>82500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>84600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>63600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>63800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>55400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>61700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>56500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>50600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>48200</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E10" s="3">
         <v>50500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>67300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>90300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>81000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>78100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>119500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>99800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>87200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>88400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>102700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>105700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>88700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>88100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>96600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>93300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>88500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>78400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>79900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>73800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>70900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>61600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>68300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>52700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>54100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>50700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>53900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>50800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>47400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>39400</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1094,100 +1106,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E12" s="3">
         <v>31900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>27600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>26500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>26900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>27800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>24600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>25400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>28300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>28900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>27700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>30200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>28100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>27400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>27000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>25000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>24700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>21900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>20300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>17400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>16200</v>
-      </c>
-      <c r="X12" s="3">
-        <v>14900</v>
       </c>
       <c r="Y12" s="3">
         <v>14900</v>
       </c>
       <c r="Z12" s="3">
+        <v>14900</v>
+      </c>
+      <c r="AA12" s="3">
         <v>15000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>15200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>13700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>13900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>14200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>13200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1278,192 +1294,201 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>200</v>
+      </c>
+      <c r="E14" s="3">
         <v>10500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>8900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>9100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>14400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>8000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>400</v>
-      </c>
-      <c r="S14" s="3">
-        <v>2400</v>
       </c>
       <c r="T14" s="3">
         <v>2400</v>
       </c>
       <c r="U14" s="3">
+        <v>2400</v>
+      </c>
+      <c r="V14" s="3">
         <v>900</v>
-      </c>
-      <c r="V14" s="3">
-        <v>100</v>
       </c>
       <c r="W14" s="3">
         <v>100</v>
       </c>
       <c r="X14" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y14" s="3">
         <v>900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E15" s="3">
         <v>12500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>12600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>12800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>13500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>14600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>14500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>16100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>16000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>13700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>13100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>12700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>7600</v>
-      </c>
-      <c r="P15" s="3">
-        <v>7700</v>
       </c>
       <c r="Q15" s="3">
         <v>7700</v>
       </c>
       <c r="R15" s="3">
+        <v>7700</v>
+      </c>
+      <c r="S15" s="3">
         <v>7800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>8000</v>
-      </c>
-      <c r="T15" s="3">
-        <v>7000</v>
       </c>
       <c r="U15" s="3">
         <v>7000</v>
       </c>
       <c r="V15" s="3">
+        <v>7000</v>
+      </c>
+      <c r="W15" s="3">
         <v>6800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>6900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>7200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>7400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>7100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>5800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>5600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>5500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>4900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1493,192 +1518,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>251400</v>
+      </c>
+      <c r="E17" s="3">
         <v>221200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>262100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>261500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>237100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>234800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>262100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>243100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>220800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>230600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>228400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>235500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>192800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>187000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>191300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>181800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>173200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>160100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>156100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>152600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>139200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>130200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>134000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>109500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>107000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>95700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>102600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>95600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>89100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>83900</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-53900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-40200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-8900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-7500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>27600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>10000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>22400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>21400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>17900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>18600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>26100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>26200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>20700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>17200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>20900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>22000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>19900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>13900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>18900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>6800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>10900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>10400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>13000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>11700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>8900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1711,468 +1743,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2800</v>
-      </c>
-      <c r="S20" s="3">
-        <v>100</v>
       </c>
       <c r="T20" s="3">
         <v>100</v>
       </c>
       <c r="U20" s="3">
+        <v>100</v>
+      </c>
+      <c r="V20" s="3">
         <v>-6100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-32900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-19200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>15000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>25300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>20800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>12900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>48400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>32400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>22400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>14500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>42500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>41500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>30500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>31000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>40700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>41600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>33300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>28600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>26300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>33500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>30800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>24400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>30300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>18300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>20200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>18900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>22400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>20100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>16700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E22" s="3">
         <v>7900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>6600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>4500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1100</v>
-      </c>
-      <c r="L22" s="3">
-        <v>600</v>
       </c>
       <c r="M22" s="3">
         <v>600</v>
       </c>
       <c r="N22" s="3">
+        <v>600</v>
+      </c>
+      <c r="O22" s="3">
         <v>500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3" t="s">
+      <c r="Q22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
       <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
         <v>2200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>100</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
       <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
         <v>2000</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>1900</v>
       </c>
       <c r="AE22" s="3">
         <v>1900</v>
       </c>
       <c r="AF22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AG22" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-63700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-49700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-14800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-13100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-15400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>22500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>21100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>21000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>17100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>18000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>27000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>28900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>20800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>17200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>12600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>19500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>16900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>10600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>16600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>10500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>9600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>11300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>10200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>7000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-13000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-6600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-10400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-2000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-8400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2263,192 +2311,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-45600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-36700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-14300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>16900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>17900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>15600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>12700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>15800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>27200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>23600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>15700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>19200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>12800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>14100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>12400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>7500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>10100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>7800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>18000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>8800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>7000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>5200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-45600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-36700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-14300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>16900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>17900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>15600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>12700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>15800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>27200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>23600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>15700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>19200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>12800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>14100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>12400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>7500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>10100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>7800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>18000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>8800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>7000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>5200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2539,8 +2596,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2589,8 +2649,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>24</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>24</v>
@@ -2610,20 +2670,20 @@
       <c r="Y29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-400</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>1300</v>
       </c>
-      <c r="AB29" s="3" t="s">
+      <c r="AC29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>24</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>24</v>
@@ -2631,8 +2691,11 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2723,8 +2786,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2815,192 +2881,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E32" s="3">
         <v>1700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2800</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-100</v>
       </c>
       <c r="T32" s="3">
         <v>-100</v>
       </c>
       <c r="U32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V32" s="3">
         <v>6100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-45600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-36700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-14300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>16900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>17900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>15600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>12700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>15800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>27200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>23600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>15700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>19200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>12800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>14100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>12400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>7500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>10100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>9100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>18000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>8800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>7000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>5200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3091,197 +3166,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-45600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-36700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-14300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>16900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>17900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>15600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>12700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>15800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>27200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>23600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>15700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>19200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>12800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>14100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>12400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>7500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>10100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>9100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>18000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>8800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>7000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>5200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45289</v>
+      </c>
+      <c r="E38" s="2">
         <v>45198</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44925</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44743</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44652</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44470</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44379</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44288</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44197</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44106</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44015</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43917</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43826</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43735</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3314,8 +3398,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3348,100 +3433,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>168600</v>
+      </c>
+      <c r="E41" s="3">
         <v>89400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>71600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>64400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>76900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>52000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>65700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>91700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>105200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>95800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>113800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>121900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>109100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>239100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>226800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>407100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>182000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>161300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>257900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>112500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>93900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>72900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>66500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>44200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>32000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>26100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>41600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>270200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>46200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>77300</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3532,376 +3621,391 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>433700</v>
+      </c>
+      <c r="E43" s="3">
         <v>480000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>507300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>502300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>479300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>494700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>447900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>367100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>320100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>301200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>291700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>264000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>240200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>207800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>210700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>214000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>193400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>177500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>176200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>170700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>168300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>153900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>143800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>141600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>123000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>121500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>113700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>96600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>96900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>85700</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>354200</v>
+      </c>
+      <c r="E44" s="3">
         <v>362900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>337200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>342800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>312000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>287600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>270300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>259600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>251300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>234400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>221600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>226800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>218400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>206000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>178100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>161900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>153600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>148500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>137100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>131700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>126400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>121200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>108600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>117100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>105900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>93300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>81100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>72100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>70100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E45" s="3">
         <v>22400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>21000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>28400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>28600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>44500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>31400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>36700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>32200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>30300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>78000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>23700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>19100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>16100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>15800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>10900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>10300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>10700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>16300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>12800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>10300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>8000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>11200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>9800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>9400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>11700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>983800</v>
+      </c>
+      <c r="E46" s="3">
         <v>954700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>937000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>937900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>896900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>878800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>815300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>755000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>708800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>661700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>643100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>626900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>645700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>676700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>634800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>795400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>545100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>503000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>582200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>425200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>399300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>364200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>331700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>313200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>268900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>252000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>246200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>448400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>224800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>232000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3992,82 +4096,85 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E48" s="3">
         <v>178100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>182600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>183400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>181700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>189700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>193600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>194700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>199400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>196500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>194900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>194100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>204500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>156700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>148400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>139800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>122500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>117300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>60000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>55900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>53100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>50800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>51000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>51300</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>51600</v>
       </c>
       <c r="AB48" s="3">
         <v>51600</v>
@@ -4076,108 +4183,114 @@
         <v>51600</v>
       </c>
       <c r="AD48" s="3">
+        <v>51600</v>
+      </c>
+      <c r="AE48" s="3">
         <v>47400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>39400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>31400</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1211400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1223600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1236100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1248700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1261500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1274900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1289400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1303200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1318400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1102500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1112500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1077300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1093600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>815300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>822800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>831400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>839200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>847400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>768300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>724300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>696300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>704200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>675300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>685700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>505500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>510700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>509900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>483700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>489100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>456600</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4268,8 +4381,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4360,100 +4476,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E52" s="3">
         <v>44400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>35600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>13800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>8300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>8000</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>2000</v>
       </c>
       <c r="AE52" s="3">
         <v>2000</v>
       </c>
       <c r="AF52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AG52" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4544,100 +4666,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2436300</v>
+      </c>
+      <c r="E54" s="3">
         <v>2400800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2391400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2383900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2348000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2349000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2304400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2259800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2230800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1965100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1955100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1903300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1949200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1653200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1610700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1771600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1512600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1473900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1417000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1212400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1156600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1127000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1064500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1056900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>835800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>822600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>815700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>981400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>755300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>722200</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4670,8 +4798,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4704,100 +4833,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>88100</v>
+      </c>
+      <c r="E57" s="3">
         <v>95800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>104000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>111200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>87200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>106600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>98700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>90300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>59400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>73400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>48000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>56600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>48200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>63100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>41900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>50100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>36000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>34900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>39000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>35200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>30800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>25700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>21300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>32900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>37600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>42200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>27500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>24300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>26200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4867,8 +5000,8 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>24</v>
+      <c r="Z58" s="3">
+        <v>0</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>24</v>
@@ -4876,11 +5009,11 @@
       <c r="AB58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
+      <c r="AC58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AD58" s="3">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AE58" s="3">
         <v>10000</v>
@@ -4888,200 +5021,209 @@
       <c r="AF58" s="3">
         <v>10000</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>137700</v>
+      </c>
+      <c r="E59" s="3">
         <v>109500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>129300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>108900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>113400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>75400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>95300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>92500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>104300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>93900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>102900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>106000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>163700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>83500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>84000</v>
-      </c>
-      <c r="R59" s="3">
-        <v>71900</v>
       </c>
       <c r="S59" s="3">
         <v>71900</v>
       </c>
       <c r="T59" s="3">
+        <v>71900</v>
+      </c>
+      <c r="U59" s="3">
         <v>59100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>59000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>58600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>62400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>57000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>50400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>46500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>36600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>33100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>45400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>39000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>32300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>225700</v>
+      </c>
+      <c r="E60" s="3">
         <v>205300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>233300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>220200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>200600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>182000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>193900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>182800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>163700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>167300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>150800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>162700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>211900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>146600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>125900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>122000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>107900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>94100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>98000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>93800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>93200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>82800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>71700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>79300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>74300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>75300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>72800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>73400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>68500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>56200</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>616500</v>
+      </c>
+      <c r="E61" s="3">
         <v>576500</v>
-      </c>
-      <c r="E61" s="3">
-        <v>511500</v>
       </c>
       <c r="F61" s="3">
         <v>511500</v>
@@ -5093,7 +5235,7 @@
         <v>511500</v>
       </c>
       <c r="I61" s="3">
-        <v>451500</v>
+        <v>511500</v>
       </c>
       <c r="J61" s="3">
         <v>451500</v>
@@ -5102,29 +5244,29 @@
         <v>451500</v>
       </c>
       <c r="L61" s="3">
-        <v>200000</v>
+        <v>451500</v>
       </c>
       <c r="M61" s="3">
         <v>200000</v>
       </c>
       <c r="N61" s="3">
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="O61" s="3">
         <v>160000</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>200000</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -5132,22 +5274,22 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>276500</v>
-      </c>
-      <c r="W61" s="3">
-        <v>240000</v>
       </c>
       <c r="X61" s="3">
         <v>240000</v>
       </c>
       <c r="Y61" s="3">
-        <v>195000</v>
+        <v>240000</v>
       </c>
       <c r="Z61" s="3">
         <v>195000</v>
       </c>
       <c r="AA61" s="3">
-        <v>0</v>
+        <v>195000</v>
       </c>
       <c r="AB61" s="3">
         <v>0</v>
@@ -5156,108 +5298,114 @@
         <v>0</v>
       </c>
       <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>176100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>180700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>180200</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>89500</v>
+      </c>
+      <c r="E62" s="3">
         <v>78100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>79900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>91300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>91800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>116600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>121800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>125100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>128500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>118300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>120200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>126700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>146700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>98700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>100000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>100200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>87700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>84500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>34200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>29700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>27400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>27600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>25900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>26800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>12300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>13000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>17500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>20500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>21300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5348,8 +5496,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5440,8 +5591,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5532,100 +5686,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>931800</v>
+      </c>
+      <c r="E66" s="3">
         <v>860000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>824700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>823000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>803900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>810100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>767200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>759400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>743700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>485600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>471000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>449300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>518500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>245300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>225900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>422200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>195600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>178600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>132200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>400000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>360600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>350400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>292600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>301200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>86600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>88300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>90300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>270000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>270600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>247600</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5658,8 +5818,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5750,8 +5911,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5842,8 +6006,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5934,8 +6101,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6026,100 +6196,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>275200</v>
+      </c>
+      <c r="E72" s="3">
         <v>320700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>357400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>365700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>360500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>371400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>385800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>368900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>364700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>367400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>374500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>356600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>340900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>328300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>312500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>285200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>261700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>246000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>226700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>213900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>199800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>187400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>180000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>169900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>166200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>157000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>139100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>130300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>123200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>118000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6210,8 +6386,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6302,8 +6481,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6394,100 +6576,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1504500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1540800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1566700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1560900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1544100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1538900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1537200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1500400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1487100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1479500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1484100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1454000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1430600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1407900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1384800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1349400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1317100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1295300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1284700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>812400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>796100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>776600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>771900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>755800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>749200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>734300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>725400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>711400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>484700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>474500</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6578,197 +6766,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45289</v>
+      </c>
+      <c r="E80" s="2">
         <v>45198</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44925</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44743</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44652</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44470</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44379</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44288</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44197</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44106</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44015</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43917</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43826</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43735</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-45600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-36700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-14300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>16900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>17900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>15600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>12700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>15800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>27200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>23600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>15700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>19200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>12800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>14100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>12400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>7500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>10100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>9100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>18000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>8800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>7000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>5200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6801,100 +6998,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E83" s="3">
         <v>22700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>22500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>23900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>27200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>23700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>23400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>24100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>21500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>20800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>20000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>11400</v>
-      </c>
-      <c r="U83" s="3">
-        <v>11600</v>
       </c>
       <c r="V83" s="3">
         <v>11600</v>
       </c>
       <c r="W83" s="3">
+        <v>11600</v>
+      </c>
+      <c r="X83" s="3">
         <v>11700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>11500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>11400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>9600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>9300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>9100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>8000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>7900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6985,8 +7186,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7077,8 +7281,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7169,8 +7376,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7261,8 +7471,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7353,100 +7566,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>45500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-39100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>12600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>35400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-66000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-19400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>27200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>23200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>23900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>22900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>28700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>30100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>32100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>24300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>26000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>26200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>25300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>20000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>25600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>8800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>8000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>9700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>24900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>14200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7479,8 +7698,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7488,91 +7708,94 @@
         <v>-8000</v>
       </c>
       <c r="E91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-8800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-13200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-9600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8800</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-7100</v>
       </c>
       <c r="W91" s="3">
         <v>-7100</v>
       </c>
       <c r="X91" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7663,8 +7886,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7755,8 +7981,11 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7764,91 +7993,94 @@
         <v>-8000</v>
       </c>
       <c r="E94" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-8800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-251300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-78500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-71600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-255900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-11500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-11300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-106100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-54400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-43600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-50000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-183100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-10000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-46900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-11600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-46500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-6200</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7881,8 +8113,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7973,8 +8206,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8065,8 +8301,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8157,8 +8396,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8249,117 +8491,123 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E100" s="3">
         <v>65000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>2400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>59900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>253800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>43100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>163200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-197600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>201600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-14600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>173900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>36000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>36300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>194800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-192100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>210800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-8500</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-300</v>
       </c>
       <c r="I101" s="3">
         <v>-300</v>
@@ -8368,38 +8616,38 @@
         <v>-300</v>
       </c>
       <c r="K101" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
-      </c>
-      <c r="O101" s="3">
-        <v>400</v>
       </c>
       <c r="P101" s="3">
         <v>400</v>
       </c>
       <c r="Q101" s="3">
+        <v>400</v>
+      </c>
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-300</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
@@ -8410,119 +8658,125 @@
         <v>0</v>
       </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>300</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>700</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>-100</v>
       </c>
       <c r="AE101" s="3">
         <v>-100</v>
       </c>
       <c r="AF101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>79300</v>
+      </c>
+      <c r="E102" s="3">
         <v>17800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-12500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>25000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-13700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-26000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-13500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>9400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-18000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-48800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-68400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>12300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-180300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>225100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>20700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-96600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>145400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>18600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>21000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>6300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>22300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>12200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>6000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-15600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-228600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>224100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-31100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-4400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MRCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MRCY_QTR_FIN.xlsx
@@ -656,424 +656,437 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45380</v>
+      </c>
+      <c r="E7" s="2">
         <v>45289</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45198</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44925</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44743</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44652</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44470</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44379</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44288</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44197</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44106</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44015</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43917</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43826</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43735</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>208300</v>
+      </c>
+      <c r="E8" s="3">
         <v>197500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>181000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>253200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>263500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>229600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>227600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>289700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>253100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>220400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>225000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>250800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>256900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>210700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>205600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>217400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>208000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>193900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>177300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>177000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>174600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>159100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>144100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>152900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>116300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>117900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>106100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>115600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>107300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>98000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>87600</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>167600</v>
+      </c>
+      <c r="E9" s="3">
         <v>165900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>130500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>185900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>173200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>148600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>149500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>170200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>153300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>133200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>136600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>148100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>151200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>122000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>117500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>120800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>114700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>105400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>98900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>97100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>100800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>88200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>82500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>84600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>63600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>63800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>55400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>61700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>56500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>50600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>48200</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E10" s="3">
         <v>31600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>50500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>67300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>90300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>81000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>78100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>119500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>99800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>87200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>88400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>102700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>105700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>88700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>88100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>96600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>93300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>88500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>78400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>79900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>73800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>70900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>61600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>68300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>52700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>54100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>50700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>53900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>50800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>47400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>39400</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1107,103 +1120,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E12" s="3">
         <v>28500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>31900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>27600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>26500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>26900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>27800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>24600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>25400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>28300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>28900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>27700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>30200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>28100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>27400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>27000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>25000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>24700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>21900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>20300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>17400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>16200</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>14900</v>
       </c>
       <c r="Z12" s="3">
         <v>14900</v>
       </c>
       <c r="AA12" s="3">
+        <v>14900</v>
+      </c>
+      <c r="AB12" s="3">
         <v>15000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>15200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>13700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>13900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>14200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>13200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1297,198 +1314,207 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E14" s="3">
         <v>200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>10500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>8900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>9100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>14400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>8000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>400</v>
-      </c>
-      <c r="T14" s="3">
-        <v>2400</v>
       </c>
       <c r="U14" s="3">
         <v>2400</v>
       </c>
       <c r="V14" s="3">
+        <v>2400</v>
+      </c>
+      <c r="W14" s="3">
         <v>900</v>
-      </c>
-      <c r="W14" s="3">
-        <v>100</v>
       </c>
       <c r="X14" s="3">
         <v>100</v>
       </c>
       <c r="Y14" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z14" s="3">
         <v>900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>2700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E15" s="3">
         <v>12300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>12500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>12600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>12800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>13500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>14600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>14500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>16100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>16000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>13700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>13100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>12700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>7600</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>7700</v>
       </c>
       <c r="R15" s="3">
         <v>7700</v>
       </c>
       <c r="S15" s="3">
+        <v>7700</v>
+      </c>
+      <c r="T15" s="3">
         <v>7800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>8000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>7000</v>
       </c>
       <c r="V15" s="3">
         <v>7000</v>
       </c>
       <c r="W15" s="3">
+        <v>7000</v>
+      </c>
+      <c r="X15" s="3">
         <v>6800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>6900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>7200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>7400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>7100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>5800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>5600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>5500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>4700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>4900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1519,198 +1545,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>253900</v>
+      </c>
+      <c r="E17" s="3">
         <v>251400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>221200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>262100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>261500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>237100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>234800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>262100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>243100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>220800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>230600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>228400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>235500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>192800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>187000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>191300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>181800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>173200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>160100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>156100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>152600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>139200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>130200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>134000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>109500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>107000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>95700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>102600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>95600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>89100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>83900</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-45600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-53900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-40200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>27600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>22400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>21400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>17900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>18600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>26100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>26200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>20700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>17200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>20900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>22000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>19900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>13900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>18900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>6800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>10900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>10400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>13000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>11700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>8900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1744,483 +1777,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2800</v>
-      </c>
-      <c r="T20" s="3">
-        <v>100</v>
       </c>
       <c r="U20" s="3">
         <v>100</v>
       </c>
       <c r="V20" s="3">
+        <v>100</v>
+      </c>
+      <c r="W20" s="3">
         <v>-6100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-26100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-32900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-19200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>15000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>25300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>20800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>12900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>48400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>32400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>22400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>14500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>42500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>41500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>30500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>31000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>40700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>41600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>33300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>28600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>26300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>33500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>30800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>24400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>30300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>18300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>20200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>18900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>22400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>20100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>16700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E22" s="3">
         <v>8700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>6700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>6600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>4500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1100</v>
-      </c>
-      <c r="M22" s="3">
-        <v>600</v>
       </c>
       <c r="N22" s="3">
         <v>600</v>
       </c>
       <c r="O22" s="3">
+        <v>600</v>
+      </c>
+      <c r="P22" s="3">
         <v>500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3" t="s">
+      <c r="R22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
       <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
         <v>2200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>100</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
-      </c>
       <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
         <v>2000</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>1900</v>
       </c>
       <c r="AF22" s="3">
         <v>1900</v>
       </c>
       <c r="AG22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AH22" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-57200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-63700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-49700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-14800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-13100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-15400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>22500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>21100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>21000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>17100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>18000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>27000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>28900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>20800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>17200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>12600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>19500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>16900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>10600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>16600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>10500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>9600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>11300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>10200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>7000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-18100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-13000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-6600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-10400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-2000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-8400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2314,198 +2363,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-44600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-45600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-36700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-14300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>16900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>17900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>15600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>12700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>15800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>27200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>23600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>15700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>19200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>12800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>14100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>12400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>7500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>10100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>7800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>18000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>8800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>7000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>5200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-44600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-45600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-36700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-14300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>16900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>17900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>15600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>12700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>15800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>27200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>23600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>15700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>19200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>12800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>14100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>12400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>7500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>10100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>7800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>18000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>8800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>7000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>5200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2599,8 +2657,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2652,8 +2713,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>24</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>24</v>
@@ -2673,20 +2734,20 @@
       <c r="Z29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-400</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>1300</v>
       </c>
-      <c r="AC29" s="3" t="s">
+      <c r="AD29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>24</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>24</v>
@@ -2694,8 +2755,11 @@
       <c r="AG29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2789,8 +2853,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2884,198 +2951,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E32" s="3">
         <v>1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2800</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-100</v>
       </c>
       <c r="U32" s="3">
         <v>-100</v>
       </c>
       <c r="V32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W32" s="3">
         <v>6100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-44600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-45600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-36700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-14300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>16900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>17900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>15600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>12700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>15800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>27200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>23600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>15700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>19200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>12800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>14100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>12400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>7500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>10100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>9100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>18000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>8800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>7000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>5200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3169,203 +3245,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-44600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-45600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-36700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-14300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>16900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>17900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>15600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>12700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>15800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>27200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>23600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>15700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>19200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>12800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>14100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>12400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>7500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>10100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>9100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>18000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>8800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>7000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>5200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45380</v>
+      </c>
+      <c r="E38" s="2">
         <v>45289</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45198</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44925</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44743</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44652</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44470</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44379</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44288</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44197</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44106</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44015</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43917</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43826</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43735</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3399,8 +3484,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3434,103 +3520,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>142600</v>
+      </c>
+      <c r="E41" s="3">
         <v>168600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>89400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>71600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>64400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>76900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>52000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>65700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>91700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>105200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>95800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>113800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>121900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>109100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>239100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>226800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>407100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>182000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>161300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>257900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>112500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>93900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>72900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>66500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>44200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>32000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>26100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>41600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>270200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>46200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>77300</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3624,388 +3714,403 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>417200</v>
+      </c>
+      <c r="E43" s="3">
         <v>433700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>480000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>507300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>502300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>479300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>494700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>447900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>367100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>320100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>301200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>291700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>264000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>240200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>207800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>210700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>214000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>193400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>177500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>176200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>170700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>168300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>153900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>143800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>141600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>123000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>121500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>113700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>96600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>96900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>85700</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>343000</v>
+      </c>
+      <c r="E44" s="3">
         <v>354200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>362900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>337200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>342800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>312000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>287600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>270300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>259600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>251300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>234400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>221600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>226800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>218400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>206000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>178100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>161900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>153600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>148500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>137100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>131700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>126400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>121200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>108600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>117100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>105900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>93300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>81100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>72100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>70100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>48600</v>
+      </c>
+      <c r="E45" s="3">
         <v>27200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>22400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>21000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>28400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>28600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>44500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>31400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>36700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>32200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>30300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>15900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>78000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>23700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>19100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>12400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>16100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>15800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>10900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>10300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>10700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>16300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>12800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>10300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>8000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>11200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>9800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>9400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>11700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>951500</v>
+      </c>
+      <c r="E46" s="3">
         <v>983800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>954700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>937000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>937900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>896900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>878800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>815300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>755000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>708800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>661700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>643100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>626900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>645700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>676700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>634800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>795400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>545100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>503000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>582200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>425200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>399300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>364200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>331700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>313200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>268900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>252000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>246200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>448400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>224800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>232000</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4099,85 +4204,88 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>177200</v>
+      </c>
+      <c r="E48" s="3">
         <v>180000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>178100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>182600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>183400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>181700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>189700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>193600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>194700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>199400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>196500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>194900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>194100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>204500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>156700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>148400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>139800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>122500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>117300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>60000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>55900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>53100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>50800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>51000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>51300</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>51600</v>
       </c>
       <c r="AC48" s="3">
         <v>51600</v>
@@ -4186,111 +4294,117 @@
         <v>51600</v>
       </c>
       <c r="AE48" s="3">
+        <v>51600</v>
+      </c>
+      <c r="AF48" s="3">
         <v>47400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>39400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>31400</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1199900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1211400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1223600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1236100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1248700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1261500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1274900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1289400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1303200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1318400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1102500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1112500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1077300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1093600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>815300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>822800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>831400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>839200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>847400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>768300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>724300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>696300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>704200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>675300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>685700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>505500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>510700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>509900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>483700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>489100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>456600</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4384,8 +4498,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4479,103 +4596,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>49500</v>
+      </c>
+      <c r="E52" s="3">
         <v>61000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>44400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>35600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>8300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>8000</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>2000</v>
       </c>
       <c r="AF52" s="3">
         <v>2000</v>
       </c>
       <c r="AG52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AH52" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4669,103 +4792,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2378200</v>
+      </c>
+      <c r="E54" s="3">
         <v>2436300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2400800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2391400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2383900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2348000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2349000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2304400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2259800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2230800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1965100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1955100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1903300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1949200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1653200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1610700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1771600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1512600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1473900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1417000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1212400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1156600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1127000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1064500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1056900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>835800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>822600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>815700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>981400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>755300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>722200</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4799,8 +4928,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4834,103 +4964,107 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>79900</v>
+      </c>
+      <c r="E57" s="3">
         <v>88100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>95800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>104000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>111200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>87200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>106600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>98700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>90300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>59400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>73400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>48000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>56600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>48200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>63100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>41900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>50100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>36000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>34900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>39000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>35200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>30800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>25700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>21300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>32900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>37600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>42200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>27500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>24300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>26200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5003,8 +5137,8 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>24</v>
+      <c r="AA58" s="3">
+        <v>0</v>
       </c>
       <c r="AB58" s="3" t="s">
         <v>24</v>
@@ -5012,11 +5146,11 @@
       <c r="AC58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
+      <c r="AD58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AE58" s="3">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AF58" s="3">
         <v>10000</v>
@@ -5024,198 +5158,207 @@
       <c r="AG58" s="3">
         <v>10000</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>127700</v>
+      </c>
+      <c r="E59" s="3">
         <v>137700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>109500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>129300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>108900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>113400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>75400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>95300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>92500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>104300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>93900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>102900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>106000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>163700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>83500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>84000</v>
-      </c>
-      <c r="S59" s="3">
-        <v>71900</v>
       </c>
       <c r="T59" s="3">
         <v>71900</v>
       </c>
       <c r="U59" s="3">
+        <v>71900</v>
+      </c>
+      <c r="V59" s="3">
         <v>59100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>59000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>58600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>62400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>57000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>50400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>46500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>36600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>33100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>45400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>39000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>32300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>207600</v>
+      </c>
+      <c r="E60" s="3">
         <v>225700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>205300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>233300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>220200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>200600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>182000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>193900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>182800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>163700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>167300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>150800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>162700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>211900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>146600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>125900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>122000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>107900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>94100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>98000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>93800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>93200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>82800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>71700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>79300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>74300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>75300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>72800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>73400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>68500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>56200</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5223,10 +5366,10 @@
         <v>616500</v>
       </c>
       <c r="E61" s="3">
+        <v>616500</v>
+      </c>
+      <c r="F61" s="3">
         <v>576500</v>
-      </c>
-      <c r="F61" s="3">
-        <v>511500</v>
       </c>
       <c r="G61" s="3">
         <v>511500</v>
@@ -5238,7 +5381,7 @@
         <v>511500</v>
       </c>
       <c r="J61" s="3">
-        <v>451500</v>
+        <v>511500</v>
       </c>
       <c r="K61" s="3">
         <v>451500</v>
@@ -5247,29 +5390,29 @@
         <v>451500</v>
       </c>
       <c r="M61" s="3">
-        <v>200000</v>
+        <v>451500</v>
       </c>
       <c r="N61" s="3">
         <v>200000</v>
       </c>
       <c r="O61" s="3">
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="P61" s="3">
         <v>160000</v>
       </c>
       <c r="Q61" s="3">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>200000</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -5277,22 +5420,22 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>276500</v>
-      </c>
-      <c r="X61" s="3">
-        <v>240000</v>
       </c>
       <c r="Y61" s="3">
         <v>240000</v>
       </c>
       <c r="Z61" s="3">
-        <v>195000</v>
+        <v>240000</v>
       </c>
       <c r="AA61" s="3">
         <v>195000</v>
       </c>
       <c r="AB61" s="3">
-        <v>0</v>
+        <v>195000</v>
       </c>
       <c r="AC61" s="3">
         <v>0</v>
@@ -5301,111 +5444,117 @@
         <v>0</v>
       </c>
       <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>176100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>180700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>180200</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>81300</v>
+      </c>
+      <c r="E62" s="3">
         <v>89500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>78100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>79900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>91300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>91800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>116600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>121800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>125100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>128500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>118300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>120200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>126700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>146700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>98700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>100000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>100200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>87700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>84500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>34200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>29700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>27400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>27600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>25900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>26800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>12300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>13000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>17500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>20500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>21300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5499,8 +5648,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5594,8 +5746,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5689,103 +5844,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>905400</v>
+      </c>
+      <c r="E66" s="3">
         <v>931800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>860000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>824700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>823000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>803900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>810100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>767200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>759400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>743700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>485600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>471000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>449300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>518500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>245300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>225900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>422200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>195600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>178600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>132200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>400000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>360600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>350400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>292600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>301200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>86600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>88300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>90300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>270000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>270600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>247600</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5819,8 +5980,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5914,8 +6076,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6009,8 +6174,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6104,8 +6272,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6199,103 +6370,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>230600</v>
+      </c>
+      <c r="E72" s="3">
         <v>275200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>320700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>357400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>365700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>360500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>371400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>385800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>368900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>364700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>367400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>374500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>356600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>340900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>328300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>312500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>285200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>261700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>246000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>226700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>213900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>199800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>187400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>180000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>169900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>166200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>157000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>139100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>130300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>123200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>118000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6389,8 +6566,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6484,8 +6664,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6579,103 +6762,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1472800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1504500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1540800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1566700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1560900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1544100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1538900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1537200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1500400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1487100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1479500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1484100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1454000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1430600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1407900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1384800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1349400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1317100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1295300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1284700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>812400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>796100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>776600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>771900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>755800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>749200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>734300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>725400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>711400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>484700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>474500</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6769,203 +6958,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45380</v>
+      </c>
+      <c r="E80" s="2">
         <v>45289</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45198</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44925</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44743</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44652</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44470</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44379</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44288</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44197</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44106</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44015</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43917</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43826</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43735</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-44600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-45600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-36700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-14300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>16900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>17900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>15600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>12700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>15800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>27200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>23600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>15700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>19200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>12800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>14100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>12400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>7500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>10100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>9100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>18000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>8800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>7000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>5200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6999,103 +7197,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E83" s="3">
         <v>22200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>22700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>22500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>23900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>27200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>23700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>23400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>24500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>24100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>21500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>20800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>20000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>13000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>11400</v>
-      </c>
-      <c r="V83" s="3">
-        <v>11600</v>
       </c>
       <c r="W83" s="3">
         <v>11600</v>
       </c>
       <c r="X83" s="3">
+        <v>11600</v>
+      </c>
+      <c r="Y83" s="3">
         <v>11700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>11500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>11400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>9600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>9300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>9100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>8000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>7900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7189,8 +7391,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7284,8 +7489,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7379,8 +7587,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7474,8 +7685,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7569,103 +7783,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E89" s="3">
         <v>45500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-39100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>12600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>35400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-66000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-19400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>27200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>23200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>23900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>22900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>28700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>30100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>32100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>24300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>26000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>26200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>25300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>20000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>25600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>8800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>8000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>9700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>24900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>14200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7699,103 +7919,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-8000</v>
+        <v>-7900</v>
       </c>
       <c r="E91" s="3">
         <v>-8000</v>
       </c>
       <c r="F91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="G91" s="3">
         <v>-8800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-10900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-9600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-8800</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-7100</v>
       </c>
       <c r="X91" s="3">
         <v>-7100</v>
       </c>
       <c r="Y91" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7889,8 +8113,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7984,103 +8211,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-8000</v>
+        <v>-7900</v>
       </c>
       <c r="E94" s="3">
         <v>-8000</v>
       </c>
       <c r="F94" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="G94" s="3">
         <v>-8800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-251300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-78500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-71600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-255900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-11000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-11500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-11300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-106100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-54400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-43600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-50000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-183100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-10000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-46900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-11600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-46500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-6200</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8114,8 +8347,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8209,8 +8443,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8304,8 +8541,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8399,8 +8639,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8494,123 +8737,129 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>41200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>65000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>2400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>59900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>253800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>43100</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>163200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-197600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>201600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-14600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>173900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>36000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>36300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>194800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-192100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>210800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-8500</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-300</v>
       </c>
       <c r="J101" s="3">
         <v>-300</v>
@@ -8619,38 +8868,38 @@
         <v>-300</v>
       </c>
       <c r="L101" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
-      </c>
-      <c r="P101" s="3">
-        <v>400</v>
       </c>
       <c r="Q101" s="3">
         <v>400</v>
       </c>
       <c r="R101" s="3">
+        <v>400</v>
+      </c>
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-300</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
@@ -8661,122 +8910,128 @@
         <v>0</v>
       </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>300</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>700</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>-100</v>
       </c>
       <c r="AF101" s="3">
         <v>-100</v>
       </c>
       <c r="AG101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E102" s="3">
         <v>79300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>17800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-12500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>25000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-13700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-26000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-13500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>9400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-18000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-48800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-68400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>12300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-180300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>225100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>20700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-96600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>145400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>18600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>21000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>6300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>22300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>12200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>6000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-15600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-228600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>224100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-31100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-4400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MRCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MRCY_QTR_FIN.xlsx
@@ -656,437 +656,450 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45471</v>
+      </c>
+      <c r="E7" s="2">
         <v>45380</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45289</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45198</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44925</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44743</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44652</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44470</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44379</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44288</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44197</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44106</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44015</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43917</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43826</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43735</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>248600</v>
+      </c>
+      <c r="E8" s="3">
         <v>208300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>197500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>181000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>253200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>263500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>229600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>227600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>289700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>253100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>220400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>225000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>250800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>256900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>210700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>205600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>217400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>208000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>193900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>177300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>177000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>174600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>159100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>144100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>152900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>116300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>117900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>106100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>115600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>107300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>98000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>87600</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>175400</v>
+      </c>
+      <c r="E9" s="3">
         <v>167600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>165900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>130500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>185900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>173200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>148600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>149500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>170200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>153300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>133200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>136600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>148100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>151200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>122000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>117500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>120800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>114700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>105400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>98900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>97100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>100800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>88200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>82500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>84600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>63600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>63800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>55400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>61700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>56500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>50600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>48200</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>73200</v>
+      </c>
+      <c r="E10" s="3">
         <v>40700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>31600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>50500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>67300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>90300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>81000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>78100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>119500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>99800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>87200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>88400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>102700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>105700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>88700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>88100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>96600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>93300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>88500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>78400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>79900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>73800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>70900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>61600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>68300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>52700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>54100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>50700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>53900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>50800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>47400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>39400</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1121,106 +1134,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E12" s="3">
         <v>21600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>28500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>31900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>27600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>26500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>26900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>27800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>24600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>25400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>28300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>28900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>27700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>30200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>28100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>27400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>27000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>25000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>24700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>21900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>20300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>17400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>16200</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>14900</v>
       </c>
       <c r="AA12" s="3">
         <v>14900</v>
       </c>
       <c r="AB12" s="3">
+        <v>14900</v>
+      </c>
+      <c r="AC12" s="3">
         <v>15000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>15200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>13700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>13900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>14200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>13200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1317,204 +1334,213 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E14" s="3">
         <v>10000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>10500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>8900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>14400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>8000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>400</v>
-      </c>
-      <c r="U14" s="3">
-        <v>2400</v>
       </c>
       <c r="V14" s="3">
         <v>2400</v>
       </c>
       <c r="W14" s="3">
+        <v>2400</v>
+      </c>
+      <c r="X14" s="3">
         <v>900</v>
-      </c>
-      <c r="X14" s="3">
-        <v>100</v>
       </c>
       <c r="Y14" s="3">
         <v>100</v>
       </c>
       <c r="Z14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA14" s="3">
         <v>900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E15" s="3">
         <v>11500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>12300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>12500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>12600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>12800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>13500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>14600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>14500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>16100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>16000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>13700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>13100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>12700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>7600</v>
-      </c>
-      <c r="R15" s="3">
-        <v>7700</v>
       </c>
       <c r="S15" s="3">
         <v>7700</v>
       </c>
       <c r="T15" s="3">
+        <v>7700</v>
+      </c>
+      <c r="U15" s="3">
         <v>7800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>8000</v>
-      </c>
-      <c r="V15" s="3">
-        <v>7000</v>
       </c>
       <c r="W15" s="3">
         <v>7000</v>
       </c>
       <c r="X15" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Y15" s="3">
         <v>6800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>6900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>7200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>7400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>7100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>5800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>5600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>5500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>4700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>4900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1546,204 +1572,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>256500</v>
+      </c>
+      <c r="E17" s="3">
         <v>253900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>251400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>221200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>262100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>261500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>237100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>234800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>262100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>243100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>220800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>230600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>228400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>235500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>192800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>187000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>191300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>181800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>173200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>160100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>156100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>152600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>139200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>130200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>134000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>109500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>107000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>95700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>102600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>95600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>89100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>83900</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-45600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-53900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-40200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>27600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>22400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>21400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>17900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>18600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>26100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>26200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>20700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>17200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>20900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>22000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>19900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>13900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>18900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>6800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>10900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>10400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>13000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>11700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>8900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1778,498 +1811,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2800</v>
-      </c>
-      <c r="U20" s="3">
-        <v>100</v>
       </c>
       <c r="V20" s="3">
         <v>100</v>
       </c>
       <c r="W20" s="3">
+        <v>100</v>
+      </c>
+      <c r="X20" s="3">
         <v>-6100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-26100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-32900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-19200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>15000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>25300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>20800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>12900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>48400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>32400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>22400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>14500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>42500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>41500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>30500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>31000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>40700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>41600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>33300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>28600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>26300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>33500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>30800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>24400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>30300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>18300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>20200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>18900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>22400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>20100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>16700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E22" s="3">
         <v>9300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>8700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>6700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1100</v>
-      </c>
-      <c r="N22" s="3">
-        <v>600</v>
       </c>
       <c r="O22" s="3">
         <v>600</v>
       </c>
       <c r="P22" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q22" s="3">
         <v>500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3" t="s">
+      <c r="S22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
       <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
         <v>2200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>100</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
       <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
         <v>2000</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>1900</v>
       </c>
       <c r="AG22" s="3">
         <v>1900</v>
       </c>
       <c r="AH22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AI22" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-18600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-57200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-63700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-49700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-14800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-13100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-15400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>22500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>21100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>21000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>17100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>18000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>27000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>28900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>20800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>17200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>12600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>19500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>16900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>10600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>16600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>5900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>10500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>9600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>11300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>10200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>7000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-12600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-18100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-13000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-6600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-10400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-2200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-2000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>6500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-8400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2366,204 +2415,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-44600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-45600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-36700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-14300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>16900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>17900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>15600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>12700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>15800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>27200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>23600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>15700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>19200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>12800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>14100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>12400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>7500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>10100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>7800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>18000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>8800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>7000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>5200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-44600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-45600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-36700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-14300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>16900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>17900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>15600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>12700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>15800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>27200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>23600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>15700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>19200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>12800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>14100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>12400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>7500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>10100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>7800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>18000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>8800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>7000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>5200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2660,8 +2718,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2716,8 +2777,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>24</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>24</v>
@@ -2737,20 +2798,20 @@
       <c r="AA29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-400</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>1300</v>
       </c>
-      <c r="AD29" s="3" t="s">
+      <c r="AE29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>24</v>
+      <c r="AF29" s="3">
+        <v>0</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>24</v>
@@ -2758,8 +2819,11 @@
       <c r="AH29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2856,8 +2920,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2954,204 +3021,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E32" s="3">
         <v>2300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2800</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-100</v>
       </c>
       <c r="V32" s="3">
         <v>-100</v>
       </c>
       <c r="W32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X32" s="3">
         <v>6100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-44600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-45600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-36700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-10900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-14300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>16900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>17900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>15600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>12700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>15800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>27200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>23600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>15700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>19200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>12800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>14100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>12400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>7500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>10100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>9100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>18000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>8800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>7000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>5200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3248,209 +3324,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-44600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-45600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-36700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-10900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-14300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>16900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>17900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>15600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>12700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>15800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>27200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>23600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>15700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>19200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>12800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>14100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>12400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>7500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>10100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>9100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>18000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>8800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>7000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>5200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45471</v>
+      </c>
+      <c r="E38" s="2">
         <v>45380</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45289</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45198</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44925</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44743</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44652</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44470</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44379</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44288</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44197</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44106</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44015</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43917</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43826</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43735</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3485,8 +3570,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3521,106 +3607,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>180500</v>
+      </c>
+      <c r="E41" s="3">
         <v>142600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>168600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>89400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>71600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>64400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>76900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>52000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>65700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>91700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>105200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>95800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>113800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>121900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>109100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>239100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>226800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>407100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>182000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>161300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>257900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>112500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>93900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>72900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>66500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>44200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>32000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>26100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>41600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>270200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>46200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>77300</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3717,400 +3807,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>415500</v>
+      </c>
+      <c r="E43" s="3">
         <v>417200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>433700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>480000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>507300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>502300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>479300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>494700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>447900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>367100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>320100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>301200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>291700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>264000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>240200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>207800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>210700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>214000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>193400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>177500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>176200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>170700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>168300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>153900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>143800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>141600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>123000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>121500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>113700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>96600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>96900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>85700</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>335300</v>
+      </c>
+      <c r="E44" s="3">
         <v>343000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>354200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>362900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>337200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>342800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>312000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>287600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>270300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>259600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>251300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>234400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>221600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>226800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>218400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>206000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>178100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>161900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>153600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>148500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>137100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>131700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>126400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>121200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>108600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>117100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>105900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>93300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>81100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>72100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>70100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E45" s="3">
         <v>48600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>27200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>22400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>21000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>28400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>28600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>44500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>31400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>36700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>32200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>30300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>15900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>78000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>23700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>19100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>12400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>16100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>15800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>10900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>10300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>10700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>16300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>12800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>10300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>8000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>11200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>9800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>9400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>11700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>953800</v>
+      </c>
+      <c r="E46" s="3">
         <v>951500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>983800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>954700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>937000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>937900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>896900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>878800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>815300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>755000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>708800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>661700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>643100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>626900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>645700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>676700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>634800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>795400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>545100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>503000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>582200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>425200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>399300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>364200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>331700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>313200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>268900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>252000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>246200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>448400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>224800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>232000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4207,88 +4312,91 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>171200</v>
+      </c>
+      <c r="E48" s="3">
         <v>177200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>180000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>178100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>182600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>183400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>181700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>189700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>193600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>194700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>199400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>196500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>194900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>194100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>204500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>156700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>148400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>139800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>122500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>117300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>60000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>55900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>53100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>50800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>51000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>51300</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>51600</v>
       </c>
       <c r="AD48" s="3">
         <v>51600</v>
@@ -4297,114 +4405,120 @@
         <v>51600</v>
       </c>
       <c r="AF48" s="3">
+        <v>51600</v>
+      </c>
+      <c r="AG48" s="3">
         <v>47400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>39400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>31400</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1188600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1199900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1211400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1223600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1236100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1248700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1261500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1274900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1289400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1303200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1318400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1102500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1112500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1077300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1093600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>815300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>822800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>831400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>839200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>847400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>768300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>724300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>696300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>704200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>675300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>685700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>505500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>510700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>509900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>483700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>489100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>456600</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4501,8 +4615,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4599,106 +4716,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>65300</v>
+      </c>
+      <c r="E52" s="3">
         <v>49500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>61000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>44400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>35600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>9800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>8300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>8000</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>2000</v>
       </c>
       <c r="AG52" s="3">
         <v>2000</v>
       </c>
       <c r="AH52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AI52" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4795,106 +4918,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2378900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2378200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2436300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2400800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2391400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2383900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2348000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2349000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2304400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2259800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2230800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1965100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1955100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1903300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1949200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1653200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1610700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1771600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1512600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1473900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1417000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1212400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1156600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1127000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1064500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1056900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>835800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>822600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>815700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>981400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>755300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>722200</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4929,8 +5058,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4965,106 +5095,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>81100</v>
+      </c>
+      <c r="E57" s="3">
         <v>79900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>88100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>95800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>104000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>111200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>87200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>106600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>98700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>90300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>59400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>73400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>48000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>56600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>48200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>63100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>41900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>50100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>36000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>34900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>39000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>35200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>30800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>25700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>21300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>32900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>37600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>42200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>27500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>24300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>26200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5140,8 +5274,8 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>24</v>
+      <c r="AB58" s="3">
+        <v>0</v>
       </c>
       <c r="AC58" s="3" t="s">
         <v>24</v>
@@ -5149,11 +5283,11 @@
       <c r="AD58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AE58" s="3">
-        <v>0</v>
+      <c r="AE58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AF58" s="3">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AG58" s="3">
         <v>10000</v>
@@ -5161,218 +5295,227 @@
       <c r="AH58" s="3">
         <v>10000</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>153300</v>
+      </c>
+      <c r="E59" s="3">
         <v>127700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>137700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>109500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>129300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>108900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>113400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>75400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>95300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>92500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>104300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>93900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>102900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>106000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>163700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>83500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>84000</v>
-      </c>
-      <c r="T59" s="3">
-        <v>71900</v>
       </c>
       <c r="U59" s="3">
         <v>71900</v>
       </c>
       <c r="V59" s="3">
+        <v>71900</v>
+      </c>
+      <c r="W59" s="3">
         <v>59100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>59000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>58600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>62400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>57000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>50400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>46500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>36600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>33100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>45400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>39000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>32300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>234400</v>
+      </c>
+      <c r="E60" s="3">
         <v>207600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>225700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>205300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>233300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>220200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>200600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>182000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>193900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>182800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>163700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>167300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>150800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>162700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>211900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>146600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>125900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>122000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>107900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>94100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>98000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>93800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>93200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>82800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>71700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>79300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>74300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>75300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>72800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>73400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>68500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>56200</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>616500</v>
+        <v>591500</v>
       </c>
       <c r="E61" s="3">
         <v>616500</v>
       </c>
       <c r="F61" s="3">
+        <v>616500</v>
+      </c>
+      <c r="G61" s="3">
         <v>576500</v>
-      </c>
-      <c r="G61" s="3">
-        <v>511500</v>
       </c>
       <c r="H61" s="3">
         <v>511500</v>
@@ -5384,7 +5527,7 @@
         <v>511500</v>
       </c>
       <c r="K61" s="3">
-        <v>451500</v>
+        <v>511500</v>
       </c>
       <c r="L61" s="3">
         <v>451500</v>
@@ -5393,29 +5536,29 @@
         <v>451500</v>
       </c>
       <c r="N61" s="3">
-        <v>200000</v>
+        <v>451500</v>
       </c>
       <c r="O61" s="3">
         <v>200000</v>
       </c>
       <c r="P61" s="3">
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="Q61" s="3">
         <v>160000</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>200000</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -5423,22 +5566,22 @@
         <v>0</v>
       </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>276500</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>240000</v>
       </c>
       <c r="Z61" s="3">
         <v>240000</v>
       </c>
       <c r="AA61" s="3">
-        <v>195000</v>
+        <v>240000</v>
       </c>
       <c r="AB61" s="3">
         <v>195000</v>
       </c>
       <c r="AC61" s="3">
-        <v>0</v>
+        <v>195000</v>
       </c>
       <c r="AD61" s="3">
         <v>0</v>
@@ -5447,114 +5590,120 @@
         <v>0</v>
       </c>
       <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>176100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>180700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>180200</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>80200</v>
+      </c>
+      <c r="E62" s="3">
         <v>81300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>89500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>78100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>79900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>91300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>91800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>116600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>121800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>125100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>128500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>118300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>120200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>126700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>146700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>98700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>100000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>100200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>87700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>84500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>34200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>29700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>27400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>27600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>25900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>26800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>12300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>13000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>17500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>20500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>21300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5651,8 +5800,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5749,8 +5901,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5847,106 +6002,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>906100</v>
+      </c>
+      <c r="E66" s="3">
         <v>905400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>931800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>860000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>824700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>823000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>803900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>810100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>767200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>759400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>743700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>485600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>471000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>449300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>518500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>245300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>225900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>422200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>195600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>178600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>132200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>400000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>360600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>350400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>292600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>301200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>86600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>88300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>90300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>270000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>270600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>247600</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5981,8 +6142,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6079,8 +6241,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6177,8 +6342,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6275,8 +6443,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6373,106 +6544,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>219800</v>
+      </c>
+      <c r="E72" s="3">
         <v>230600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>275200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>320700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>357400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>365700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>360500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>371400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>385800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>368900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>364700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>367400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>374500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>356600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>340900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>328300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>312500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>285200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>261700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>246000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>226700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>213900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>199800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>187400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>180000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>169900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>166200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>157000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>139100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>130300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>123200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>118000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6569,8 +6746,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6667,8 +6847,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6765,8 +6948,11 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6774,97 +6960,100 @@
         <v>1472800</v>
       </c>
       <c r="E76" s="3">
+        <v>1472800</v>
+      </c>
+      <c r="F76" s="3">
         <v>1504500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1540800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1566700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1560900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1544100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1538900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1537200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1500400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1487100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1479500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1484100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1454000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1430600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1407900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1384800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1349400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1317100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1295300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1284700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>812400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>796100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>776600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>771900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>755800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>749200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>734300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>725400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>711400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>484700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>474500</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6961,209 +7150,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45471</v>
+      </c>
+      <c r="E80" s="2">
         <v>45380</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45289</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45198</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44925</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44743</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44652</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44470</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44379</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44288</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44197</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44106</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44015</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43917</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43826</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43735</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-44600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-45600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-36700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-10900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-14300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>16900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>17900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>15600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>12700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>15800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>27200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>23600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>15700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>19200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>12800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>14100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>12400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>7500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>10100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>9100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>18000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>8800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>7000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>5200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7198,106 +7396,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E83" s="3">
         <v>21800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>22200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>22700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>22500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>23900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>27200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>23700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>23400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>24500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>24100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>21500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>20800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>20000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>13300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>13000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>11400</v>
-      </c>
-      <c r="W83" s="3">
-        <v>11600</v>
       </c>
       <c r="X83" s="3">
         <v>11600</v>
       </c>
       <c r="Y83" s="3">
+        <v>11600</v>
+      </c>
+      <c r="Z83" s="3">
         <v>11700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>11500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>12000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>11400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>9600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>9300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>9100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>8000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>7900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7394,8 +7596,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7492,8 +7697,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7590,8 +7798,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7688,8 +7899,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7786,106 +8000,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>71800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-17800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>45500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-39100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>12600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>35400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-66000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-19400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>27200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>23200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>23900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>22900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>28700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>30100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>32100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>24300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>26000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>26200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>25300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>20000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>25600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>8800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>8000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>9700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>24900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>14200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7920,106 +8140,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7900</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-8000</v>
       </c>
       <c r="F91" s="3">
         <v>-8000</v>
       </c>
       <c r="G91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="H91" s="3">
         <v>-8800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-10900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-11300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-9600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-8800</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-7100</v>
       </c>
       <c r="Y91" s="3">
         <v>-7100</v>
       </c>
       <c r="Z91" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8116,8 +8340,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8214,106 +8441,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7900</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-8000</v>
       </c>
       <c r="F94" s="3">
         <v>-8000</v>
       </c>
       <c r="G94" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="H94" s="3">
         <v>-8800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-251300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-78500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-71600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-255900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-11000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-11500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-11300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-106100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-54400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-43600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-183100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-10000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-46900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-11600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-46500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-6200</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8348,8 +8581,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8446,8 +8680,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8544,8 +8781,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8642,8 +8882,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8740,129 +8983,135 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-23500</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>41200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>65000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>2400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>59900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>253800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>43100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>163200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-197600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>201600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-14600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>173900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>36000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>36300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>194800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-192100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>210800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-8500</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>300</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-300</v>
       </c>
       <c r="K101" s="3">
         <v>-300</v>
@@ -8871,38 +9120,38 @@
         <v>-300</v>
       </c>
       <c r="M101" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-400</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>400</v>
       </c>
       <c r="R101" s="3">
         <v>400</v>
       </c>
       <c r="S101" s="3">
+        <v>400</v>
+      </c>
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-300</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
@@ -8913,125 +9162,131 @@
         <v>0</v>
       </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>300</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>700</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>-100</v>
       </c>
       <c r="AG101" s="3">
         <v>-100</v>
       </c>
       <c r="AH101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-26000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>79300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>17800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-12500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>25000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-13700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-26000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-18000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-48800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-68400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>12300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-180300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>225100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>20700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-96600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>145400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>18600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>21000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>6300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>22300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>12200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>6000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-15600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-228600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>224100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-31100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-4400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MRCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MRCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>MRCY</t>
   </si>
@@ -656,450 +656,463 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45562</v>
+      </c>
+      <c r="E7" s="2">
         <v>45471</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45380</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45289</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45198</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44925</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44743</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44652</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44470</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44379</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44288</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44197</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44106</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44015</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43917</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43826</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43735</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>204400</v>
+      </c>
+      <c r="E8" s="3">
         <v>248600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>208300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>197500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>181000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>253200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>263500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>229600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>227600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>289700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>253100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>220400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>225000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>250800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>256900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>210700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>205600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>217400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>208000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>193900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>177300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>177000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>174600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>159100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>144100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>152900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>116300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>117900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>106100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>115600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>107300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>98000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>87600</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>152600</v>
+      </c>
+      <c r="E9" s="3">
         <v>175400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>167600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>165900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>130500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>185900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>173200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>148600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>149500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>170200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>153300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>133200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>136600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>148100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>151200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>122000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>117500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>120800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>114700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>105400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>98900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>97100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>100800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>88200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>82500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>84600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>63600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>63800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>55400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>61700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>56500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>50600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>48200</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>51800</v>
+      </c>
+      <c r="E10" s="3">
         <v>73200</v>
       </c>
-      <c r="E10" s="3">
-        <v>40700</v>
-      </c>
       <c r="F10" s="3">
-        <v>31600</v>
+        <v>40600</v>
       </c>
       <c r="G10" s="3">
+        <v>31500</v>
+      </c>
+      <c r="H10" s="3">
         <v>50500</v>
       </c>
-      <c r="H10" s="3">
-        <v>67300</v>
-      </c>
       <c r="I10" s="3">
+        <v>67400</v>
+      </c>
+      <c r="J10" s="3">
         <v>90300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>81000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>78100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>119500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>99800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>87200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>88400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>102700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>105700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>88700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>88100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>96600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>93300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>88500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>78400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>79900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>73800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>70900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>61600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>68300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>52700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>54100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>50700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>53900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>50800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>47400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>39400</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1135,109 +1148,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E12" s="3">
         <v>19400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>21600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>28500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>31900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>27600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>26500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>26900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>27800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>25400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>28300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>28900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>27700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>30200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>28100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>27400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>27000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>25000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>24700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>21900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>20300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>17400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>16200</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>14900</v>
       </c>
       <c r="AB12" s="3">
         <v>14900</v>
       </c>
       <c r="AC12" s="3">
+        <v>14900</v>
+      </c>
+      <c r="AD12" s="3">
         <v>15000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>15200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>13700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>13900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>14200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>13200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1337,210 +1354,219 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>7100</v>
+        <v>2400</v>
       </c>
       <c r="E14" s="3">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="F14" s="3">
-        <v>200</v>
+        <v>12100</v>
       </c>
       <c r="G14" s="3">
-        <v>10500</v>
+        <v>1600</v>
       </c>
       <c r="H14" s="3">
+        <v>11000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J14" s="3">
+        <v>4800</v>
+      </c>
+      <c r="K14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L14" s="3">
         <v>4000</v>
       </c>
-      <c r="I14" s="3">
-        <v>4400</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="M14" s="3">
+        <v>8900</v>
+      </c>
+      <c r="N14" s="3">
+        <v>9100</v>
+      </c>
+      <c r="O14" s="3">
+        <v>6500</v>
+      </c>
+      <c r="P14" s="3">
+        <v>14400</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>8000</v>
+      </c>
+      <c r="R14" s="3">
         <v>3000</v>
       </c>
-      <c r="K14" s="3">
-        <v>4000</v>
-      </c>
-      <c r="L14" s="3">
-        <v>8900</v>
-      </c>
-      <c r="M14" s="3">
-        <v>9100</v>
-      </c>
-      <c r="N14" s="3">
-        <v>6500</v>
-      </c>
-      <c r="O14" s="3">
-        <v>14400</v>
-      </c>
-      <c r="P14" s="3">
-        <v>8000</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>3000</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>3400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>400</v>
-      </c>
-      <c r="V14" s="3">
-        <v>2400</v>
       </c>
       <c r="W14" s="3">
         <v>2400</v>
       </c>
       <c r="X14" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Y14" s="3">
         <v>900</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>100</v>
       </c>
       <c r="Z14" s="3">
         <v>100</v>
       </c>
       <c r="AA14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB14" s="3">
         <v>900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E15" s="3">
         <v>11300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>11500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>12300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>12500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>12600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>12800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>13500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>14600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>14500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>16100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>16000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>13700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>13100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>12700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>7600</v>
-      </c>
-      <c r="S15" s="3">
-        <v>7700</v>
       </c>
       <c r="T15" s="3">
         <v>7700</v>
       </c>
       <c r="U15" s="3">
+        <v>7700</v>
+      </c>
+      <c r="V15" s="3">
         <v>7800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>8000</v>
-      </c>
-      <c r="W15" s="3">
-        <v>7000</v>
       </c>
       <c r="X15" s="3">
         <v>7000</v>
       </c>
       <c r="Y15" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Z15" s="3">
         <v>6800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>6900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>7200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>7400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>7100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>5800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>5600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>5500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>4700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>4900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1573,210 +1599,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>256500</v>
+        <v>215400</v>
       </c>
       <c r="E17" s="3">
-        <v>253900</v>
+        <v>249400</v>
       </c>
       <c r="F17" s="3">
-        <v>251400</v>
+        <v>243900</v>
       </c>
       <c r="G17" s="3">
-        <v>221200</v>
+        <v>251200</v>
       </c>
       <c r="H17" s="3">
+        <v>210700</v>
+      </c>
+      <c r="I17" s="3">
+        <v>258100</v>
+      </c>
+      <c r="J17" s="3">
+        <v>257100</v>
+      </c>
+      <c r="K17" s="3">
+        <v>237100</v>
+      </c>
+      <c r="L17" s="3">
+        <v>234800</v>
+      </c>
+      <c r="M17" s="3">
         <v>262100</v>
       </c>
-      <c r="I17" s="3">
-        <v>261500</v>
-      </c>
-      <c r="J17" s="3">
-        <v>237100</v>
-      </c>
-      <c r="K17" s="3">
-        <v>234800</v>
-      </c>
-      <c r="L17" s="3">
-        <v>262100</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>243100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>220800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>230600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>228400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>235500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>192800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>187000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>191300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>181800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>173200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>160100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>156100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>152600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>139200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>130200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>134000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>109500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>107000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>95700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>102600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>95600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>89100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>83900</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-7900</v>
+        <v>-11000</v>
       </c>
       <c r="E18" s="3">
-        <v>-45600</v>
+        <v>-900</v>
       </c>
       <c r="F18" s="3">
-        <v>-53900</v>
+        <v>-35600</v>
       </c>
       <c r="G18" s="3">
-        <v>-40200</v>
+        <v>-53700</v>
       </c>
       <c r="H18" s="3">
-        <v>-8900</v>
+        <v>-29700</v>
       </c>
       <c r="I18" s="3">
-        <v>2000</v>
+        <v>-4900</v>
       </c>
       <c r="J18" s="3">
+        <v>6300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-7500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>27600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>10000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>22400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>21400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>17900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>18600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>26100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>26200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>20700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>17200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>20900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>22000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>19900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>13900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>18900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>6800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>10900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>10400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>13000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>11700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>8900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1812,513 +1845,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-1500</v>
+        <v>1300</v>
       </c>
       <c r="E20" s="3">
-        <v>-2300</v>
+        <v>-3000</v>
       </c>
       <c r="F20" s="3">
-        <v>-1200</v>
+        <v>700</v>
       </c>
       <c r="G20" s="3">
-        <v>-1700</v>
+        <v>-200</v>
       </c>
       <c r="H20" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="I20" s="3">
+        <v>600</v>
+      </c>
+      <c r="J20" s="3">
+        <v>200</v>
+      </c>
+      <c r="K20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="P20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="R20" s="3">
+        <v>100</v>
+      </c>
+      <c r="S20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="T20" s="3">
         <v>-600</v>
       </c>
-      <c r="J20" s="3">
-        <v>1100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>100</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-600</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2800</v>
-      </c>
-      <c r="V20" s="3">
-        <v>100</v>
       </c>
       <c r="W20" s="3">
         <v>100</v>
       </c>
       <c r="X20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>11900</v>
+        <v>-1100</v>
       </c>
       <c r="E21" s="3">
-        <v>-26100</v>
+        <v>13400</v>
       </c>
       <c r="F21" s="3">
-        <v>-32900</v>
+        <v>-24800</v>
       </c>
       <c r="G21" s="3">
-        <v>-19200</v>
+        <v>-41200</v>
       </c>
       <c r="H21" s="3">
-        <v>15000</v>
+        <v>-18400</v>
       </c>
       <c r="I21" s="3">
-        <v>25300</v>
+        <v>7200</v>
       </c>
       <c r="J21" s="3">
+        <v>18900</v>
+      </c>
+      <c r="K21" s="3">
         <v>20800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>12900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>48400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>32400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>22400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>14500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>42500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>41500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>30500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>31000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>40700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>41600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>33300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>28600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>26300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>33500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>30800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>24400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>30300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>18300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>20200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>18900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>22400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>20100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>16700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E22" s="3">
         <v>9200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>8700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1100</v>
-      </c>
-      <c r="O22" s="3">
-        <v>600</v>
       </c>
       <c r="P22" s="3">
         <v>600</v>
       </c>
       <c r="Q22" s="3">
+        <v>600</v>
+      </c>
+      <c r="R22" s="3">
         <v>500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3" t="s">
+      <c r="T22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
       <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
         <v>2200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>100</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
-      </c>
       <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
         <v>2000</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>1900</v>
       </c>
       <c r="AH22" s="3">
         <v>1900</v>
       </c>
       <c r="AI22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-18600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-57200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-63700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-49700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-14800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-13100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-15400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>22500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>21100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>21000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>17100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>18000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>27000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>28900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>20800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>17200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>12600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>19500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>16900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>10600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>16600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>5900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>10500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>9600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>11300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>10200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>7000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-7800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-12600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-18100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-13000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-6600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-10400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-2000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-8400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2418,210 +2467,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-44600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-45600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-36700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-8200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-14300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>16900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>17900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>15600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>12700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>15800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>27200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>23600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>15700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>19200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>12800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>14100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>12400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>7500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>10100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>7800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>18000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>8800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>7000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>5200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-44600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-45600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-36700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-8200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-14300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>16900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>17900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>15600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>12700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>15800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>27200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>23600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>15700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>19200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>12800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>14100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>12400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>7500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>10100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>7800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>18000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>8800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>7000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>5200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2721,8 +2779,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2780,8 +2841,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>24</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>24</v>
@@ -2801,20 +2862,20 @@
       <c r="AB29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-400</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>1300</v>
       </c>
-      <c r="AE29" s="3" t="s">
+      <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>24</v>
+      <c r="AG29" s="3">
+        <v>0</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>24</v>
@@ -2822,8 +2883,11 @@
       <c r="AI29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2923,8 +2987,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3024,210 +3091,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1500</v>
+        <v>-1300</v>
       </c>
       <c r="E32" s="3">
-        <v>2300</v>
+        <v>3000</v>
       </c>
       <c r="F32" s="3">
-        <v>1200</v>
+        <v>-700</v>
       </c>
       <c r="G32" s="3">
-        <v>1700</v>
+        <v>200</v>
       </c>
       <c r="H32" s="3">
-        <v>-1400</v>
+        <v>-1300</v>
       </c>
       <c r="I32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="L32" s="3">
+        <v>3600</v>
+      </c>
+      <c r="M32" s="3">
+        <v>2600</v>
+      </c>
+      <c r="N32" s="3">
+        <v>2100</v>
+      </c>
+      <c r="O32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="P32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>700</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S32" s="3">
+        <v>700</v>
+      </c>
+      <c r="T32" s="3">
         <v>600</v>
       </c>
-      <c r="J32" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>3600</v>
-      </c>
-      <c r="L32" s="3">
-        <v>2600</v>
-      </c>
-      <c r="M32" s="3">
-        <v>2100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>1300</v>
-      </c>
-      <c r="O32" s="3">
-        <v>1400</v>
-      </c>
-      <c r="P32" s="3">
-        <v>700</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>700</v>
-      </c>
-      <c r="S32" s="3">
-        <v>600</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2800</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-100</v>
       </c>
       <c r="W32" s="3">
         <v>-100</v>
       </c>
       <c r="X32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y32" s="3">
         <v>6100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-44600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-45600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-36700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-14300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>16900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>17900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>15600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>12700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>15800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>27200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>23600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>15700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>19200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>12800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>14100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>12400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>7500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>10100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>9100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>18000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>8800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>7000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>5200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3327,215 +3403,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-44600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-45600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-36700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-14300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>16900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>17900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>15600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>12700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>15800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>27200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>23600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>15700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>19200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>12800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>14100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>12400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>7500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>10100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>9100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>18000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>8800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>7000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>5200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45562</v>
+      </c>
+      <c r="E38" s="2">
         <v>45471</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45380</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45289</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45198</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44925</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44743</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44652</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44470</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44379</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44288</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44197</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44106</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44015</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43917</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43826</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43735</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3571,8 +3656,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3608,109 +3694,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>158100</v>
+      </c>
+      <c r="E41" s="3">
         <v>180500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>142600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>168600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>89400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>71600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>64400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>76900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>52000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>65700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>91700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>105200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>95800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>113800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>121900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>109100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>239100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>226800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>407100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>182000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>161300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>257900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>112500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>93900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>72900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>66500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>44200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>32000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>26100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>41600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>270200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>46200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>77300</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3810,435 +3900,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>422800</v>
+      </c>
+      <c r="E43" s="3">
         <v>415500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>417200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>433700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>480000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>507300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>502300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>479300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>494700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>447900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>367100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>320100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>301200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>291700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>264000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>240200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>207800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>210700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>214000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>193400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>177500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>176200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>170700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>168300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>153900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>143800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>141600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>123000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>121500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>113700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>96600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>96900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>85700</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>351100</v>
+      </c>
+      <c r="E44" s="3">
         <v>335300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>343000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>354200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>362900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>337200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>342800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>312000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>287600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>270300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>259600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>251300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>234400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>221600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>226800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>218400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>206000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>178100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>161900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>153600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>148500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>137100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>131700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>126400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>121200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>108600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>117100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>105900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>93300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>81100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>72100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>70100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>22500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>48600</v>
+      <c r="D45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="F45" s="3">
-        <v>27200</v>
+        <v>28000</v>
       </c>
       <c r="G45" s="3">
-        <v>22400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>21000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>28400</v>
+        <v>5800</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="J45" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K45" s="3">
         <v>28600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>44500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>31400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>36700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>32200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>30300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>15900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>78000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>23700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>19100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>12400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>16100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>15800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>10900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>10300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>10700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>16300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>12800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>10300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>8000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>11200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>9800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>9400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>11700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>954300</v>
+      </c>
+      <c r="E46" s="3">
         <v>953800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>951500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>983800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>954700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>937000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>937900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>896900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>878800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>815300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>755000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>708800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>661700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>643100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>626900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>645700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>676700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>634800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>795400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>545100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>503000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>582200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>425200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>399300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>364200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>331700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>313200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>268900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>252000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>246200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>448400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>224800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>232000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
+        <v>3600</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>3500</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4315,91 +4420,94 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>163400</v>
+      </c>
+      <c r="E48" s="3">
         <v>171200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>177200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>180000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>178100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>182600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>183400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>181700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>189700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>193600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>194700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>199400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>196500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>194900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>194100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>204500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>156700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>148400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>139800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>122500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>117300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>60000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>55900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>53100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>50800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>51000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>51300</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>51600</v>
       </c>
       <c r="AE48" s="3">
         <v>51600</v>
@@ -4408,117 +4516,123 @@
         <v>51600</v>
       </c>
       <c r="AG48" s="3">
+        <v>51600</v>
+      </c>
+      <c r="AH48" s="3">
         <v>47400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>39400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>31400</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1177400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1188600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1199900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1211400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1223600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1236100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1248700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1261500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1274900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1289400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1303200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1318400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1102500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1112500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1077300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1093600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>815300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>822800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>831400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>839200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>847400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>768300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>724300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>696300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>704200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>675300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>685700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>505500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>510700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>509900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>483700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>489100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>456600</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4618,8 +4732,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4719,109 +4836,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>65300</v>
+        <v>7500</v>
       </c>
       <c r="E52" s="3">
-        <v>49500</v>
+        <v>6700</v>
       </c>
       <c r="F52" s="3">
-        <v>61000</v>
+        <v>1500</v>
       </c>
       <c r="G52" s="3">
-        <v>44400</v>
+        <v>5600</v>
       </c>
       <c r="H52" s="3">
-        <v>35600</v>
+        <v>4400</v>
       </c>
       <c r="I52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J52" s="3">
         <v>13800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>9800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>8300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8000</v>
-      </c>
-      <c r="AG52" s="3">
-        <v>2000</v>
       </c>
       <c r="AH52" s="3">
         <v>2000</v>
       </c>
       <c r="AI52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4921,109 +5044,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2369000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2378900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2378200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2436300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2400800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2391400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2383900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2348000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2349000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2304400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2259800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2230800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1965100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1955100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1903300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1949200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1653200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1610700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1771600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1512600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1473900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1417000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1212400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1156600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1127000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1064500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1056900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>835800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>822600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>815700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>981400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>755300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>722200</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5059,8 +5188,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5096,129 +5226,133 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>74700</v>
+      </c>
+      <c r="E57" s="3">
         <v>81100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>79900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>88100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>95800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>104000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>111200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>87200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>106600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>98700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>90300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>59400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>73400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>48000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>56600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>48200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>63100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>41900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>50100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>36000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>34900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>39000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>35200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>30800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>25700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>21300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>32900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>37600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>42200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>27500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>24300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>26200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>15500</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>11600</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>14600</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>14200</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>10400</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -5277,8 +5411,8 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>24</v>
+      <c r="AC58" s="3">
+        <v>0</v>
       </c>
       <c r="AD58" s="3" t="s">
         <v>24</v>
@@ -5286,11 +5420,11 @@
       <c r="AE58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF58" s="3">
-        <v>0</v>
+      <c r="AF58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AG58" s="3">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AH58" s="3">
         <v>10000</v>
@@ -5298,239 +5432,248 @@
       <c r="AI58" s="3">
         <v>10000</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>10000</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>153300</v>
+        <v>107100</v>
       </c>
       <c r="E59" s="3">
-        <v>127700</v>
+        <v>93100</v>
       </c>
       <c r="F59" s="3">
-        <v>137700</v>
+        <v>83500</v>
       </c>
       <c r="G59" s="3">
-        <v>109500</v>
+        <v>84700</v>
       </c>
       <c r="H59" s="3">
-        <v>129300</v>
+        <v>65100</v>
       </c>
       <c r="I59" s="3">
-        <v>108900</v>
+        <v>73200</v>
       </c>
       <c r="J59" s="3">
+        <v>56900</v>
+      </c>
+      <c r="K59" s="3">
         <v>113400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>75400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>95300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>92500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>104300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>93900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>102900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>106000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>163700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>83500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>84000</v>
-      </c>
-      <c r="U59" s="3">
-        <v>71900</v>
       </c>
       <c r="V59" s="3">
         <v>71900</v>
       </c>
       <c r="W59" s="3">
+        <v>71900</v>
+      </c>
+      <c r="X59" s="3">
         <v>59100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>59000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>58600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>62400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>57000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>50400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>46500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>36600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>33100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>45400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>39000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>32300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>232800</v>
+      </c>
+      <c r="E60" s="3">
         <v>234400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>207600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>225700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>205300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>233300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>220200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>200600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>182000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>193900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>182800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>163700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>167300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>150800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>162700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>211900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>146600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>125900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>122000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>107900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>94100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>98000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>93800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>93200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>82800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>71700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>79300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>74300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>75300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>72800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>73400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>68500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>56200</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>591500</v>
+        <v>660900</v>
       </c>
       <c r="E61" s="3">
-        <v>616500</v>
+        <v>656500</v>
       </c>
       <c r="F61" s="3">
-        <v>616500</v>
+        <v>685600</v>
       </c>
       <c r="G61" s="3">
-        <v>576500</v>
+        <v>693500</v>
       </c>
       <c r="H61" s="3">
-        <v>511500</v>
+        <v>642200</v>
       </c>
       <c r="I61" s="3">
-        <v>511500</v>
+        <v>578300</v>
       </c>
       <c r="J61" s="3">
-        <v>511500</v>
+        <v>582800</v>
       </c>
       <c r="K61" s="3">
         <v>511500</v>
       </c>
       <c r="L61" s="3">
-        <v>451500</v>
+        <v>511500</v>
       </c>
       <c r="M61" s="3">
         <v>451500</v>
@@ -5539,29 +5682,29 @@
         <v>451500</v>
       </c>
       <c r="O61" s="3">
-        <v>200000</v>
+        <v>451500</v>
       </c>
       <c r="P61" s="3">
         <v>200000</v>
       </c>
       <c r="Q61" s="3">
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="R61" s="3">
         <v>160000</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>200000</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -5569,22 +5712,22 @@
         <v>0</v>
       </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>276500</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>240000</v>
       </c>
       <c r="AA61" s="3">
         <v>240000</v>
       </c>
       <c r="AB61" s="3">
-        <v>195000</v>
+        <v>240000</v>
       </c>
       <c r="AC61" s="3">
         <v>195000</v>
       </c>
       <c r="AD61" s="3">
-        <v>0</v>
+        <v>195000</v>
       </c>
       <c r="AE61" s="3">
         <v>0</v>
@@ -5593,117 +5736,123 @@
         <v>0</v>
       </c>
       <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>176100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>180700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>180200</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>80200</v>
+        <v>9500</v>
       </c>
       <c r="E62" s="3">
-        <v>81300</v>
+        <v>9700</v>
       </c>
       <c r="F62" s="3">
-        <v>89500</v>
+        <v>7500</v>
       </c>
       <c r="G62" s="3">
-        <v>78100</v>
+        <v>7600</v>
       </c>
       <c r="H62" s="3">
-        <v>79900</v>
+        <v>7900</v>
       </c>
       <c r="I62" s="3">
-        <v>91300</v>
+        <v>8400</v>
       </c>
       <c r="J62" s="3">
+        <v>8400</v>
+      </c>
+      <c r="K62" s="3">
         <v>91800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>116600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>121800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>125100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>128500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>118300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>120200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>126700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>146700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>98700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>100000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>100200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>87700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>84500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>34200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>29700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>27400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>27600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>25900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>26800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>12300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>13000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>17500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>20500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>21300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5803,8 +5952,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5904,8 +6056,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6005,109 +6160,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>909100</v>
+      </c>
+      <c r="E66" s="3">
         <v>906100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>905400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>931800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>860000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>824700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>823000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>803900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>810100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>767200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>759400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>743700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>485600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>471000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>449300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>518500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>245300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>225900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>422200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>195600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>178600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>132200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>400000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>360600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>350400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>292600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>301200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>86600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>88300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>90300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>270000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>270600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>247600</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6143,8 +6304,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6244,8 +6406,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6345,8 +6510,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6446,8 +6614,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6547,109 +6718,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>202300</v>
+      </c>
+      <c r="E72" s="3">
         <v>219800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>230600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>275200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>320700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>357400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>365700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>360500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>371400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>385800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>368900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>364700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>367400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>374500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>356600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>340900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>328300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>312500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>285200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>261700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>246000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>226700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>213900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>199800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>187400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>180000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>169900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>166200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>157000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>139100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>130300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>123200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>118000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6749,8 +6926,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6850,8 +7030,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6951,109 +7134,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1472800</v>
+        <v>1459800</v>
       </c>
       <c r="E76" s="3">
         <v>1472800</v>
       </c>
       <c r="F76" s="3">
+        <v>1472800</v>
+      </c>
+      <c r="G76" s="3">
         <v>1504500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1540800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1566700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1560900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1544100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1538900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1537200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1500400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1487100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1479500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1484100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1454000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1430600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1407900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1384800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1349400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1317100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1295300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1284700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>812400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>796100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>776600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>771900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>755800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>749200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>734300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>725400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>711400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>484700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>474500</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7153,215 +7342,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45562</v>
+      </c>
+      <c r="E80" s="2">
         <v>45471</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45380</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45289</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45198</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44925</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44743</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44652</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44470</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44379</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44288</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44197</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44106</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44015</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43917</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43826</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43735</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-44600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-45600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-36700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-14300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>16900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>17900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>15600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>12700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>15800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>27200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>23600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>15700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>19200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>12800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>14100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>12400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>7500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>10100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>9100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>18000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>8800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>7000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>5200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7397,109 +7595,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>21400</v>
+        <v>10100</v>
       </c>
       <c r="E83" s="3">
-        <v>21800</v>
+        <v>9900</v>
       </c>
       <c r="F83" s="3">
-        <v>22200</v>
+        <v>11100</v>
       </c>
       <c r="G83" s="3">
-        <v>22700</v>
+        <v>13700</v>
       </c>
       <c r="H83" s="3">
-        <v>22500</v>
+        <v>9100</v>
       </c>
       <c r="I83" s="3">
-        <v>23900</v>
+        <v>8900</v>
       </c>
       <c r="J83" s="3">
+        <v>8400</v>
+      </c>
+      <c r="K83" s="3">
         <v>27200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>23700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>23400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>24500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>24100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>21500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>20800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>20000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>13300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>13000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>11400</v>
-      </c>
-      <c r="X83" s="3">
-        <v>11600</v>
       </c>
       <c r="Y83" s="3">
         <v>11600</v>
       </c>
       <c r="Z83" s="3">
+        <v>11600</v>
+      </c>
+      <c r="AA83" s="3">
         <v>11700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>11500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>12000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>11400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>9600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>9300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>9100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>8000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>7900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7599,8 +7801,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7700,8 +7905,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7801,8 +8009,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7902,8 +8113,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8003,109 +8217,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E89" s="3">
         <v>71800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-17800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>45500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-39100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>12600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>35400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-66000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-19400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>27200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>23200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>23900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>22900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>28700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>30100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>32100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>24300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>26000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>26200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>25300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>20000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>25600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>8800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>8000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>9700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>24900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>14200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8141,109 +8361,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7900</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-8000</v>
       </c>
       <c r="G91" s="3">
         <v>-8000</v>
       </c>
       <c r="H91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-8800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-11300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-9600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-8800</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-7100</v>
       </c>
       <c r="Z91" s="3">
         <v>-7100</v>
       </c>
       <c r="AA91" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8343,8 +8567,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8444,109 +8671,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7900</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-8000</v>
       </c>
       <c r="G94" s="3">
         <v>-8000</v>
       </c>
       <c r="H94" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="I94" s="3">
         <v>-8800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-251300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-78500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-71600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-255900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-11000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-11500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-11300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-106100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-54400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-43600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-183100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-10000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-46900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-11600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-46500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-6200</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8582,31 +8815,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8683,8 +8917,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8784,8 +9021,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8885,8 +9125,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8986,135 +9229,141 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-23500</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>41200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>65000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>2400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>59900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>253800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-7300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>43100</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>163200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-197600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>201600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-14600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>173900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>36000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>36300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>194800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-192100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>210800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-8500</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
+        <v>200</v>
+      </c>
+      <c r="F101" s="3">
+        <v>100</v>
+      </c>
+      <c r="G101" s="3">
+        <v>300</v>
+      </c>
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
-        <v>600</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H101" s="3">
-        <v>200</v>
-      </c>
       <c r="I101" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="J101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K101" s="3">
         <v>300</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-300</v>
       </c>
       <c r="L101" s="3">
         <v>-300</v>
@@ -9123,38 +9372,38 @@
         <v>-300</v>
       </c>
       <c r="N101" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-400</v>
-      </c>
-      <c r="R101" s="3">
-        <v>400</v>
       </c>
       <c r="S101" s="3">
         <v>400</v>
       </c>
       <c r="T101" s="3">
+        <v>400</v>
+      </c>
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-300</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
         <v>0</v>
       </c>
@@ -9165,128 +9414,134 @@
         <v>0</v>
       </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>300</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>700</v>
-      </c>
-      <c r="AG101" s="3">
-        <v>-100</v>
       </c>
       <c r="AH101" s="3">
         <v>-100</v>
       </c>
       <c r="AI101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="E102" s="3">
         <v>37900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-26000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>79300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>17800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-12500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>25000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-13700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-26000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>9400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-18000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-48800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-68400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>12300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-180300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>225100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>20700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-96600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>145400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>18600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>21000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>6300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>22300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>12200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>6000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-15600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-228600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>224100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-31100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-4400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MRCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MRCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
   <si>
     <t>MRCY</t>
   </si>
@@ -656,463 +656,475 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45653</v>
+      </c>
+      <c r="E7" s="2">
         <v>45562</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45471</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45380</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45289</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45198</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44925</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44743</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44652</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44470</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44379</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44288</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44197</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44106</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44015</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43917</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43826</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43735</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>223100</v>
+      </c>
+      <c r="E8" s="3">
         <v>204400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>248600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>208300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>197500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>181000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>253200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>263500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>229600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>227600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>289700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>253100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>220400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>225000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>250800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>256900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>210700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>205600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>217400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>208000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>193900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>177300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>177000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>174600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>159100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>144100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>152900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>116300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>117900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>106100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>115600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>107300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>98000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>87600</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>162300</v>
+      </c>
+      <c r="E9" s="3">
         <v>152600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>175400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>167600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>165900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>130500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>185900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>173200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>148600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>149500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>170200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>153300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>133200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>136600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>148100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>151200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>122000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>117500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>120800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>114700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>105400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>98900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>97100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>100800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>88200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>82500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>84600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>63600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>63800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>55400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>61700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>56500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>50600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>48200</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>60800</v>
+      </c>
+      <c r="E10" s="3">
         <v>51800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>73200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>40600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>31500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>50500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>67400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>90300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>81000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>78100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>119500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>99800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>87200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>88400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>102700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>105700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>88700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>88100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>96600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>93300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>88500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>78400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>79900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>73800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>70900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>61600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>68300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>52700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>54100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>50700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>53900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>50800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>47400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>39400</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1149,112 +1161,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E12" s="3">
         <v>18400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>19400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>21600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>28500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>31900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>27600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>26500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>26900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>27800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>24600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>25400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>28300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>28900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>27700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>30200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>28100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>27400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>27000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>25000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>24700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>21900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>20300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>17400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>16200</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>14900</v>
       </c>
       <c r="AC12" s="3">
         <v>14900</v>
       </c>
       <c r="AD12" s="3">
+        <v>14900</v>
+      </c>
+      <c r="AE12" s="3">
         <v>15000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>15200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>13700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>13900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>14200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>13200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1357,112 +1373,118 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>200</v>
+      </c>
+      <c r="E14" s="3">
         <v>2400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>8000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>12100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>11000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>8900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>6500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>14400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>8000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>3000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>400</v>
-      </c>
-      <c r="W14" s="3">
-        <v>2400</v>
       </c>
       <c r="X14" s="3">
         <v>2400</v>
       </c>
       <c r="Y14" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Z14" s="3">
         <v>900</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>100</v>
       </c>
       <c r="AA14" s="3">
         <v>100</v>
       </c>
       <c r="AB14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC14" s="3">
         <v>900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>2700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>900</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1470,103 +1492,106 @@
         <v>11200</v>
       </c>
       <c r="E15" s="3">
+        <v>11200</v>
+      </c>
+      <c r="F15" s="3">
         <v>11300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>12300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>12500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>12600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>12800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>13500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>14600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>14500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>16100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>16000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>13700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>13100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>12700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>7600</v>
-      </c>
-      <c r="T15" s="3">
-        <v>7700</v>
       </c>
       <c r="U15" s="3">
         <v>7700</v>
       </c>
       <c r="V15" s="3">
+        <v>7700</v>
+      </c>
+      <c r="W15" s="3">
         <v>7800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>8000</v>
-      </c>
-      <c r="X15" s="3">
-        <v>7000</v>
       </c>
       <c r="Y15" s="3">
         <v>7000</v>
       </c>
       <c r="Z15" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AA15" s="3">
         <v>6800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>6900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>7200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>7400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>7100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>5800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>5600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>5500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>4700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>4900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1600,216 +1625,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>235300</v>
+      </c>
+      <c r="E17" s="3">
         <v>215400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>249400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>243900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>251200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>210700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>258100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>257100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>237100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>234800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>262100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>243100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>220800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>230600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>228400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>235500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>192800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>187000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>191300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>181800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>173200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>160100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>156100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>152600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>139200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>130200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>134000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>109500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>107000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>95700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>102600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>95600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>89100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>83900</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-11000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-35600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-53700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-29700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>27600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>22400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>21400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>17900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>18600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>26100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>26200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>20700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>17200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>20900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>22000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>19900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>13900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>18900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>6800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>10900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>10400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>13000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>11700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>8900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1846,528 +1878,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E20" s="3">
         <v>1300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2800</v>
-      </c>
-      <c r="W20" s="3">
-        <v>100</v>
       </c>
       <c r="X20" s="3">
         <v>100</v>
       </c>
       <c r="Y20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>13400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-24800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-41200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-18400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>18900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>20800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>12900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>48400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>32400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>22400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>14500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>42500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>41500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>30500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>31000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>40700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>41600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>33300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>28600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>26300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>33500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>30800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>24400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>30300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>18300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>20200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>18900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>22400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>20100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>16700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E22" s="3">
         <v>8900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>9300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>8700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>6600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1100</v>
-      </c>
-      <c r="P22" s="3">
-        <v>600</v>
       </c>
       <c r="Q22" s="3">
         <v>600</v>
       </c>
       <c r="R22" s="3">
+        <v>600</v>
+      </c>
+      <c r="S22" s="3">
         <v>500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3" t="s">
+      <c r="U22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>100</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
       <c r="X22" s="3">
         <v>0</v>
       </c>
       <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
         <v>2200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>100</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
-      </c>
       <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
         <v>2000</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>1900</v>
       </c>
       <c r="AI22" s="3">
         <v>1900</v>
       </c>
       <c r="AJ22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AK22" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-23100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-18600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-57200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-63700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-49700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-14800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-15400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>22500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>21100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>21000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>17100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>18000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>27000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>28900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>20800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>17200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>12600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>19500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>16900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>10600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>16600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>10500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>9600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>11300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>10200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E24" s="3">
         <v>-5600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-7800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-12600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-18100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-13000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-6600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-10400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-2200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>6500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-8400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2470,216 +2518,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-44600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-45600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-36700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-14300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>16900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>17900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>15600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>12700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>15800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>27200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>23600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>15700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>19200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>12800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>14100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>12400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>7500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>10100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>7800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>18000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>8800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>7000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>5200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-44600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-45600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-36700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>16900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>17900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>15600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>12700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>15800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>27200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>23600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>15700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>19200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>12800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>14100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>12400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>7500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>10100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>7800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>18000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>8800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>7000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>5200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2782,8 +2839,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2844,8 +2904,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>24</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>24</v>
@@ -2865,20 +2925,20 @@
       <c r="AC29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-400</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>1300</v>
       </c>
-      <c r="AF29" s="3" t="s">
+      <c r="AG29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>24</v>
+      <c r="AH29" s="3">
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>24</v>
@@ -2886,8 +2946,11 @@
       <c r="AJ29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2990,8 +3053,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3094,216 +3160,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2800</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-100</v>
       </c>
       <c r="X32" s="3">
         <v>-100</v>
       </c>
       <c r="Y32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z32" s="3">
         <v>6100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-44600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-45600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-36700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>16900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>17900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>15600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>12700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>15800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>27200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>23600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>15700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>19200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>12800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>14100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>12400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>7500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>10100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>9100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>18000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>8800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>7000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>5200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3406,221 +3481,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-44600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-45600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-36700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>16900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>17900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>15600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>12700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>15800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>27200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>23600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>15700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>19200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>12800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>14100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>12400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>7500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>10100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>9100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>18000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>8800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>7000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>5200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45653</v>
+      </c>
+      <c r="E38" s="2">
         <v>45562</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45471</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45380</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45289</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45198</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44925</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44743</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44652</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44470</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44379</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44288</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44197</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44106</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44015</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43917</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43826</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43735</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3657,8 +3741,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3695,112 +3780,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>242600</v>
+      </c>
+      <c r="E41" s="3">
         <v>158100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>180500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>142600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>168600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>89400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>71600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>64400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>76900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>52000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>65700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>91700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>105200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>95800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>113800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>121900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>109100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>239100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>226800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>407100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>182000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>161300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>257900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>112500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>93900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>72900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>66500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>44200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>32000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>26100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>41600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>270200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>46200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>77300</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3903,216 +3992,225 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>383100</v>
+      </c>
+      <c r="E43" s="3">
         <v>422800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>415500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>417200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>433700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>480000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>507300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>502300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>479300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>494700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>447900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>367100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>320100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>301200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>291700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>264000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>240200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>207800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>210700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>214000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>193400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>177500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>176200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>170700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>168300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>153900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>143800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>141600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>123000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>121500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>113700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>96600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>96900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>85700</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>344400</v>
+      </c>
+      <c r="E44" s="3">
         <v>351100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>335300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>343000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>354200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>362900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>337200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>342800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>312000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>287600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>270300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>259600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>251300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>234400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>221600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>226800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>218400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>206000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>178100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>161900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>153600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>148500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>137100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>131700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>126400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>121200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>108600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>117100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>105900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>93300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>81100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>72100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>70100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4122,205 +4220,211 @@
       <c r="E45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G45" s="3">
         <v>28000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5800</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K45" s="3">
         <v>3600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>28600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>44500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>31400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>36700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>32200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>30300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>15900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>14200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>78000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>23700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>19100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>12400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>16100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>15800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>10900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>10300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>10700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>16300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>12800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>10300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>8000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>11200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>9800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>9400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>11700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>990700</v>
+      </c>
+      <c r="E46" s="3">
         <v>954300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>953800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>951500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>983800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>954700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>937000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>937900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>896900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>878800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>815300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>755000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>708800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>661700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>643100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>626900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>645700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>676700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>634800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>795400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>545100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>503000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>582200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>425200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>399300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>364200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>331700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>313200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>268900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>252000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>246200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>448400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>224800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>232000</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4330,24 +4434,24 @@
       <c r="E47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G47" s="3">
         <v>3600</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" s="3">
         <v>3500</v>
       </c>
-      <c r="J47" s="3" t="s">
+      <c r="K47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -4423,94 +4527,97 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E48" s="3">
         <v>163400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>171200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>177200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>180000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>178100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>182600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>183400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>181700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>189700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>193600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>194700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>199400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>196500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>194900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>194100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>204500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>156700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>148400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>139800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>122500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>117300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>60000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>55900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>53100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>50800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>51000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>51300</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>51600</v>
       </c>
       <c r="AF48" s="3">
         <v>51600</v>
@@ -4519,120 +4626,126 @@
         <v>51600</v>
       </c>
       <c r="AH48" s="3">
+        <v>51600</v>
+      </c>
+      <c r="AI48" s="3">
         <v>47400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>39400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>31400</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1164200</v>
+      </c>
+      <c r="E49" s="3">
         <v>1177400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1188600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1199900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1211400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1223600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1236100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1248700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1261500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1274900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1289400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1303200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1318400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1102500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1112500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1077300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1093600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>815300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>822800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>831400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>839200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>847400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>768300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>724300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>696300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>704200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>675300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>685700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>505500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>510700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>509900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>483700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>489100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>456600</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4735,8 +4848,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4839,112 +4955,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E52" s="3">
         <v>7500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>13800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>8000</v>
-      </c>
-      <c r="AH52" s="3">
-        <v>2000</v>
       </c>
       <c r="AI52" s="3">
         <v>2000</v>
       </c>
       <c r="AJ52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AK52" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5047,112 +5169,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2401500</v>
+      </c>
+      <c r="E54" s="3">
         <v>2369000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2378900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2378200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2436300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2400800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2391400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2383900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2348000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2349000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2304400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2259800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2230800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1965100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1955100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1903300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1949200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1653200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1610700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1771600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1512600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1473900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1417000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1212400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1156600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1127000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1064500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1056900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>835800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>822600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>815700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>981400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>755300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>722200</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5189,8 +5317,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5227,136 +5356,140 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>64800</v>
+      </c>
+      <c r="E57" s="3">
         <v>74700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>81100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>79900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>88100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>95800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>104000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>111200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>87200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>106600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>98700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>90300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>59400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>73400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>48000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>56600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>48200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>63100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>41900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>50100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>36000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>34900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>39000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>35200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>30800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>25700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>21300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>32900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>37600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>42200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>27500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>24300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>26200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>15500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>15000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>14600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>14200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10400</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -5414,8 +5547,8 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>24</v>
+      <c r="AD58" s="3">
+        <v>0</v>
       </c>
       <c r="AE58" s="3" t="s">
         <v>24</v>
@@ -5423,11 +5556,11 @@
       <c r="AF58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG58" s="3">
-        <v>0</v>
+      <c r="AG58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AH58" s="3">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AI58" s="3">
         <v>10000</v>
@@ -5435,248 +5568,257 @@
       <c r="AJ58" s="3">
         <v>10000</v>
       </c>
+      <c r="AK58" s="3">
+        <v>10000</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>142300</v>
+      </c>
+      <c r="E59" s="3">
         <v>107100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>93100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>83500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>84700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>65100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>73200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>56900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>113400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>75400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>95300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>92500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>104300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>93900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>102900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>106000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>163700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>83500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>84000</v>
-      </c>
-      <c r="V59" s="3">
-        <v>71900</v>
       </c>
       <c r="W59" s="3">
         <v>71900</v>
       </c>
       <c r="X59" s="3">
+        <v>71900</v>
+      </c>
+      <c r="Y59" s="3">
         <v>59100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>59000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>58600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>62400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>57000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>50400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>46500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>36600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>33100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>45400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>39000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>32300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>273500</v>
+      </c>
+      <c r="E60" s="3">
         <v>232800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>234400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>207600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>225700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>205300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>233300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>220200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>200600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>182000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>193900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>182800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>163700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>167300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>150800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>162700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>211900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>146600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>125900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>122000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>107900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>94100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>98000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>93800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>93200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>82800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>71700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>79300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>74300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>75300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>72800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>73400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>68500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>56200</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>652900</v>
+      </c>
+      <c r="E61" s="3">
         <v>660900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>656500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>685600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>693500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>642200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>578300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>582800</v>
-      </c>
-      <c r="K61" s="3">
-        <v>511500</v>
       </c>
       <c r="L61" s="3">
         <v>511500</v>
       </c>
       <c r="M61" s="3">
-        <v>451500</v>
+        <v>511500</v>
       </c>
       <c r="N61" s="3">
         <v>451500</v>
@@ -5685,29 +5827,29 @@
         <v>451500</v>
       </c>
       <c r="P61" s="3">
-        <v>200000</v>
+        <v>451500</v>
       </c>
       <c r="Q61" s="3">
         <v>200000</v>
       </c>
       <c r="R61" s="3">
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="S61" s="3">
         <v>160000</v>
       </c>
       <c r="T61" s="3">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>200000</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -5715,22 +5857,22 @@
         <v>0</v>
       </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>276500</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>240000</v>
       </c>
       <c r="AB61" s="3">
         <v>240000</v>
       </c>
       <c r="AC61" s="3">
-        <v>195000</v>
+        <v>240000</v>
       </c>
       <c r="AD61" s="3">
         <v>195000</v>
       </c>
       <c r="AE61" s="3">
-        <v>0</v>
+        <v>195000</v>
       </c>
       <c r="AF61" s="3">
         <v>0</v>
@@ -5739,120 +5881,126 @@
         <v>0</v>
       </c>
       <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
         <v>176100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>180700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>180200</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E62" s="3">
         <v>9500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7900</v>
-      </c>
-      <c r="I62" s="3">
-        <v>8400</v>
       </c>
       <c r="J62" s="3">
         <v>8400</v>
       </c>
       <c r="K62" s="3">
+        <v>8400</v>
+      </c>
+      <c r="L62" s="3">
         <v>91800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>116600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>121800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>125100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>128500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>118300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>120200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>126700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>146700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>98700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>100000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>100200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>87700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>84500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>34200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>29700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>27400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>27600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>25900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>26800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>12300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>13000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>17500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>20500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>21300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5955,8 +6103,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6059,8 +6210,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6163,112 +6317,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>941200</v>
+      </c>
+      <c r="E66" s="3">
         <v>909100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>906100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>905400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>931800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>860000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>824700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>823000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>803900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>810100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>767200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>759400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>743700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>485600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>471000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>449300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>518500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>245300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>225900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>422200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>195600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>178600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>132200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>400000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>360600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>350400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>292600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>301200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>86600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>88300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>90300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>270000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>270600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>247600</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6305,8 +6465,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6409,8 +6570,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6513,8 +6677,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6617,8 +6784,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6721,112 +6891,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>184700</v>
+      </c>
+      <c r="E72" s="3">
         <v>202300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>219800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>230600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>275200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>320700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>357400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>365700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>360500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>371400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>385800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>368900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>364700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>367400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>374500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>356600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>340900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>328300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>312500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>285200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>261700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>246000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>226700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>213900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>199800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>187400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>180000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>169900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>166200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>157000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>139100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>130300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>123200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>118000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6929,8 +7105,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7033,8 +7212,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7137,112 +7319,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1460300</v>
+      </c>
+      <c r="E76" s="3">
         <v>1459800</v>
-      </c>
-      <c r="E76" s="3">
-        <v>1472800</v>
       </c>
       <c r="F76" s="3">
         <v>1472800</v>
       </c>
       <c r="G76" s="3">
+        <v>1472800</v>
+      </c>
+      <c r="H76" s="3">
         <v>1504500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1540800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1566700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1560900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1544100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1538900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1537200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1500400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1487100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1479500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1484100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1454000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1430600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1407900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1384800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1349400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1317100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1295300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1284700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>812400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>796100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>776600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>771900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>755800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>749200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>734300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>725400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>711400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>484700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>474500</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7345,221 +7533,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45653</v>
+      </c>
+      <c r="E80" s="2">
         <v>45562</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45471</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45380</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45289</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45198</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44925</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44743</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44652</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44470</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44379</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44288</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44197</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44106</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44015</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43917</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43826</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43735</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-44600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-45600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-36700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>16900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>17900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>15600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>12700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>15800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>27200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>23600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>15700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>19200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>12800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>14100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>12400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>7500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>10100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>9100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>18000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>8800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>7000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>5200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7596,112 +7793,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E83" s="3">
         <v>10100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>9900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>13700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>8900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>27200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>23700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>23400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>24500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>24100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>21500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>20800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>20000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>13300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>13000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>11400</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>11600</v>
       </c>
       <c r="Z83" s="3">
         <v>11600</v>
       </c>
       <c r="AA83" s="3">
+        <v>11600</v>
+      </c>
+      <c r="AB83" s="3">
         <v>11700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>11500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>12000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>11400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>9600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>9300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>9100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>8000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7804,8 +8005,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7908,8 +8112,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8012,8 +8219,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8116,8 +8326,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8220,112 +8433,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>85500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-14700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>71800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-17800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>45500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-39100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>12600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>35400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-66000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-19400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>27200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>23200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>23900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>22900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>28700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>30100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>32100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>24300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>26000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>26200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>25300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>20000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>25600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>8800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>8000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>9700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>24900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>14200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8362,112 +8581,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7900</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-8000</v>
       </c>
       <c r="H91" s="3">
         <v>-8000</v>
       </c>
       <c r="I91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="J91" s="3">
         <v>-8800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-11500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-10900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-11300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-9600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-8800</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-7100</v>
       </c>
       <c r="AA91" s="3">
         <v>-7100</v>
       </c>
       <c r="AB91" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8570,8 +8793,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8674,112 +8900,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7900</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-8000</v>
       </c>
       <c r="H94" s="3">
         <v>-8000</v>
       </c>
       <c r="I94" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="J94" s="3">
         <v>-8800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-251300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-78500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-71600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-255900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-11000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-11500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-11300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-106100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-54400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-43600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-183100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-10000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-46900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-11600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-46500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-6200</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8816,8 +9048,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8842,8 +9075,8 @@
       <c r="J96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8920,8 +9153,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9024,8 +9260,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9128,8 +9367,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9232,129 +9474,135 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-23500</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>41200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>65000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>2400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>59900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>253800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>43100</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>163200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-197600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>201600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-14600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>173900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>36000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>36300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>194800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-192100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>210800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-8500</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-300</v>
       </c>
       <c r="I101" s="3">
         <v>-300</v>
@@ -9363,10 +9611,10 @@
         <v>-300</v>
       </c>
       <c r="K101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L101" s="3">
         <v>300</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-300</v>
       </c>
       <c r="M101" s="3">
         <v>-300</v>
@@ -9375,38 +9623,38 @@
         <v>-300</v>
       </c>
       <c r="O101" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-400</v>
-      </c>
-      <c r="S101" s="3">
-        <v>400</v>
       </c>
       <c r="T101" s="3">
         <v>400</v>
       </c>
       <c r="U101" s="3">
+        <v>400</v>
+      </c>
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-300</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
         <v>0</v>
       </c>
@@ -9417,131 +9665,137 @@
         <v>0</v>
       </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>300</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>700</v>
-      </c>
-      <c r="AH101" s="3">
-        <v>-100</v>
       </c>
       <c r="AI101" s="3">
         <v>-100</v>
       </c>
       <c r="AJ101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>84400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-22400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>37900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-26000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>79300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>17800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-12500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>25000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-26000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>9400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-48800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-68400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>12300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-180300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>225100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>20700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-96600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>145400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>18600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>21000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>6300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>22300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>12200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>6000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-15600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-228600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>224100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-31100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-4400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MRCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MRCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
   <si>
     <t>MRCY</t>
   </si>
@@ -656,475 +656,488 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45744</v>
+      </c>
+      <c r="E7" s="2">
         <v>45653</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45562</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45471</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45380</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45289</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45198</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44925</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44743</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44652</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44470</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44379</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44288</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44197</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44106</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44015</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43917</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43826</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>211400</v>
+      </c>
+      <c r="E8" s="3">
         <v>223100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>204400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>248600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>208300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>197500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>181000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>253200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>263500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>229600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>227600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>289700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>253100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>220400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>225000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>250800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>256900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>210700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>205600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>217400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>208000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>193900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>177300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>177000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>174600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>159100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>144100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>152900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>116300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>117900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>106100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>115600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>107300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>98000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>87600</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>154200</v>
+      </c>
+      <c r="E9" s="3">
         <v>162300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>152600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>175400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>167600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>165900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>130500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>185900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>173200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>148600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>149500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>170200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>153300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>133200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>136600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>148100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>151200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>122000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>117500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>120800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>114700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>105400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>98900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>97100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>100800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>88200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>82500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>84600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>63600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>63800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>55400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>61700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>56500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>50600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>48200</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>57100</v>
+      </c>
+      <c r="E10" s="3">
         <v>60800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>51800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>73200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>40600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>31500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>50500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>67400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>90300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>81000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>78100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>119500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>99800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>87200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>88400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>102700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>105700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>88700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>88100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>96600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>93300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>88500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>78400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>79900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>73800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>70900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>61600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>68300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>52700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>54100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>50700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>53900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>50800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>47400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>39400</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1162,115 +1175,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E12" s="3">
         <v>21400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>18400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>19400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>21600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>28500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>31900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>27600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>26500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>26900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>27800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>24600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>25400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>28300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>28900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>27700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>30200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>28100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>27400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>27000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>25000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>24700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>21900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>20300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>17400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>16200</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>14900</v>
       </c>
       <c r="AD12" s="3">
         <v>14900</v>
       </c>
       <c r="AE12" s="3">
+        <v>14900</v>
+      </c>
+      <c r="AF12" s="3">
         <v>15000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>15200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>13700</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>13900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>14200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>13200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1376,222 +1393,231 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>200</v>
+        <v>3000</v>
       </c>
       <c r="E14" s="3">
+        <v>300</v>
+      </c>
+      <c r="F14" s="3">
         <v>2400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>8000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>12100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>11000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>8900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>9100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>6500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>14400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>8000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>3400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>400</v>
-      </c>
-      <c r="X14" s="3">
-        <v>2400</v>
       </c>
       <c r="Y14" s="3">
         <v>2400</v>
       </c>
       <c r="Z14" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AA14" s="3">
         <v>900</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>100</v>
       </c>
       <c r="AB14" s="3">
         <v>100</v>
       </c>
       <c r="AC14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD14" s="3">
         <v>900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>400</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>900</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>1100</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>11200</v>
+        <v>10200</v>
       </c>
       <c r="E15" s="3">
         <v>11200</v>
       </c>
       <c r="F15" s="3">
+        <v>11200</v>
+      </c>
+      <c r="G15" s="3">
         <v>11300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>12300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>12500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>12600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>13500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>14600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>14500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>16100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>16000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>13700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>13100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>12700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>7600</v>
-      </c>
-      <c r="U15" s="3">
-        <v>7700</v>
       </c>
       <c r="V15" s="3">
         <v>7700</v>
       </c>
       <c r="W15" s="3">
+        <v>7700</v>
+      </c>
+      <c r="X15" s="3">
         <v>7800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>8000</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>7000</v>
       </c>
       <c r="Z15" s="3">
         <v>7000</v>
       </c>
       <c r="AA15" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AB15" s="3">
         <v>6800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>6900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>7200</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>7400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>7100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>5800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>5600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>5500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>4900</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1626,222 +1652,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>223500</v>
+      </c>
+      <c r="E17" s="3">
         <v>235300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>215400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>249400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>243900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>251200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>210700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>258100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>257100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>237100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>234800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>262100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>243100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>220800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>230600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>228400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>235500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>192800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>187000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>191300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>181800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>173200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>160100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>156100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>152600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>139200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>130200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>134000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>109500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>107000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>95700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>102600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>95600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>89100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>83900</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-12200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-11000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-35600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-53700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-29700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>27600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>22400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>21400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>17900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>18600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>26100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>26200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>20700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>17200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>20900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>22000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>19900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>13900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>18900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>6800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>10900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>10400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>13000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>11700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>8900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1879,543 +1912,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>3900</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F20" s="3">
         <v>1300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>700</v>
       </c>
-      <c r="H20" s="3">
-        <v>-200</v>
-      </c>
       <c r="I20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J20" s="3">
         <v>1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2800</v>
-      </c>
-      <c r="X20" s="3">
-        <v>100</v>
       </c>
       <c r="Y20" s="3">
         <v>100</v>
       </c>
       <c r="Z20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-4900</v>
+        <v>-1800</v>
       </c>
       <c r="E21" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>13400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-24800</v>
       </c>
-      <c r="H21" s="3">
-        <v>-41200</v>
-      </c>
       <c r="I21" s="3">
+        <v>-40400</v>
+      </c>
+      <c r="J21" s="3">
         <v>-18400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>7200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>18900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>20800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>12900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>48400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>32400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>22400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>14500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>42500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>41500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>30500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>31000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>40700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>41600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>33300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>28600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>26300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>33500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>30800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>24400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>30300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>18300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>20200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>18900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>22400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>20100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>16700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E22" s="3">
         <v>8400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>8900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>9200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>8700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>6700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>6600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>600</v>
       </c>
       <c r="R22" s="3">
         <v>600</v>
       </c>
       <c r="S22" s="3">
+        <v>600</v>
+      </c>
+      <c r="T22" s="3">
         <v>500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3" t="s">
+      <c r="V22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>100</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
       <c r="Y22" s="3">
         <v>0</v>
       </c>
       <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
         <v>2200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>100</v>
       </c>
-      <c r="AG22" s="3">
-        <v>0</v>
-      </c>
       <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
         <v>2000</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>1900</v>
       </c>
       <c r="AJ22" s="3">
         <v>1900</v>
       </c>
       <c r="AK22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AL22" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-24300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-23100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-18600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-57200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-63700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-49700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-13100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-15400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>22500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>21100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>21000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>17100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>18000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>27000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>28900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>20800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>17200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>12600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>19500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>16900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>10600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>16600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>10500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>9600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>11300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>7000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-6700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-5600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-7800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-12600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-18100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-13000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-6600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-10400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>6500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-8400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2521,222 +2570,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-17500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-44600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-45600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-36700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-14300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>16900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>17900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>15600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>12700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>15800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>27200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>23600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>15700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>19200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>12800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>14100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>12400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>7500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>10100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>7800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>18000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>8800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>5200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-17500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-44600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-45600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-36700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>16900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>17900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>15600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>12700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>15800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>27200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>23600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>15700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>19200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>12800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>14100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>12400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>7500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>10100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>7800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>18000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>8800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>5200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2842,8 +2900,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2968,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>24</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>24</v>
@@ -2928,20 +2989,20 @@
       <c r="AD29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-400</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>1300</v>
       </c>
-      <c r="AG29" s="3" t="s">
+      <c r="AH29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>24</v>
+      <c r="AI29" s="3">
+        <v>0</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>24</v>
@@ -2949,8 +3010,11 @@
       <c r="AK29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3056,8 +3120,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3163,222 +3230,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-3900</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-700</v>
       </c>
-      <c r="H32" s="3">
-        <v>200</v>
-      </c>
       <c r="I32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J32" s="3">
         <v>-1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2800</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-100</v>
       </c>
       <c r="Y32" s="3">
         <v>-100</v>
       </c>
       <c r="Z32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA32" s="3">
         <v>6100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-17500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-44600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-45600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-36700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-14300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>16900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>17900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>15600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>12700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>15800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>27200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>23600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>15700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>19200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>12800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>14100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>12400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>7500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>10100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>9100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>18000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>8800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>5200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3484,227 +3560,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-17500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-44600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-45600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-36700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-14300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>16900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>17900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>15600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>12700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>15800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>27200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>23600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>15700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>19200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>12800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>14100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>12400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>7500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>10100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>9100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>18000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>8800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>5200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45744</v>
+      </c>
+      <c r="E38" s="2">
         <v>45653</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45562</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45471</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45380</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45289</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45198</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44925</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44743</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44652</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44470</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44379</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44288</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44197</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44106</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44015</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43917</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43826</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3742,8 +3827,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3781,115 +3867,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>269800</v>
+      </c>
+      <c r="E41" s="3">
         <v>242600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>158100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>180500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>142600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>168600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>89400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>71600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>64400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>76900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>52000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>65700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>91700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>105200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>95800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>113800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>121900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>109100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>239100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>226800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>407100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>182000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>161300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>257900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>112500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>93900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>72900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>66500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>44200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>32000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>26100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>41600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>270200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>46200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>77300</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3995,227 +4085,236 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>374700</v>
+      </c>
+      <c r="E43" s="3">
         <v>383100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>422800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>415500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>417200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>433700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>480000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>507300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>502300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>479300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>494700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>447900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>367100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>320100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>301200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>291700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>264000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>240200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>207800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>210700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>214000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>193400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>177500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>176200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>170700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>168300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>153900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>143800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>141600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>123000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>121500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>113700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>96600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>96900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>85700</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>352700</v>
+      </c>
+      <c r="E44" s="3">
         <v>344400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>351100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>335300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>343000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>354200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>362900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>337200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>342800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>312000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>287600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>270300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>259600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>251300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>234400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>221600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>226800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>218400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>206000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>178100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>161900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>153600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>148500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>137100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>131700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>126400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>121200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>108600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>117100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>105900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>93300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>81100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>72100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>70100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>24</v>
+      <c r="D45" s="3">
+        <v>3000</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>24</v>
@@ -4223,208 +4322,214 @@
       <c r="F45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H45" s="3">
         <v>28000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5800</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="3">
         <v>3600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>28600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>44500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>31400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>36700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>32200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>30300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>15900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>14200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>78000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>23700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>19100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>12400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>16100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>15800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>10900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>10300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>10700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>16300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>12800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>10300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>8000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>11200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>9800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>9400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>11700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1019500</v>
+      </c>
+      <c r="E46" s="3">
         <v>990700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>954300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>953800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>951500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>983800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>954700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>937000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>937900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>896900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>878800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>815300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>755000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>708800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>661700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>643100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>626900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>645700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>676700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>634800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>795400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>545100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>503000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>582200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>425200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>399300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>364200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>331700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>313200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>268900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>252000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>246200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>448400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>224800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>232000</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4437,24 +4542,24 @@
       <c r="F47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H47" s="3">
         <v>3600</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K47" s="3">
         <v>3500</v>
       </c>
-      <c r="K47" s="3" t="s">
+      <c r="L47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -4530,97 +4635,100 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>162100</v>
+      </c>
+      <c r="E48" s="3">
         <v>168000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>163400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>171200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>177200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>180000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>178100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>182600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>183400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>181700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>189700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>193600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>194700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>199400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>196500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>194900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>194100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>204500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>156700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>148400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>139800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>122500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>117300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>60000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>55900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>53100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>50800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>51000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>51300</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>51600</v>
       </c>
       <c r="AG48" s="3">
         <v>51600</v>
@@ -4629,123 +4737,129 @@
         <v>51600</v>
       </c>
       <c r="AI48" s="3">
+        <v>51600</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>47400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>39400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>31400</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1154100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1164200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1177400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1188600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1199900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1211400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1223600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1236100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1248700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1261500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1274900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1289400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1303200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1318400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1102500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1112500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1077300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1093600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>815300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>822800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>831400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>839200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>847400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>768300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>724300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>696300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>704200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>675300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>685700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>505500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>510700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>509900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>483700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>489100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>456600</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4851,8 +4965,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4958,115 +5075,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E52" s="3">
         <v>6800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>6800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>8300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>8000</v>
-      </c>
-      <c r="AI52" s="3">
-        <v>2000</v>
       </c>
       <c r="AJ52" s="3">
         <v>2000</v>
       </c>
       <c r="AK52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AL52" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5172,115 +5295,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2414400</v>
+      </c>
+      <c r="E54" s="3">
         <v>2401500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2369000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2378900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2378200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2436300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2400800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2391400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2383900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2348000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2349000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2304400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2259800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2230800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1965100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1955100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1903300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1949200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1653200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1610700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1771600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1512600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1473900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1417000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1212400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1156600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1127000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1064500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1056900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>835800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>822600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>815700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>981400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>755300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>722200</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5318,8 +5447,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5357,115 +5487,119 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>73600</v>
+      </c>
+      <c r="E57" s="3">
         <v>64800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>74700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>81100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>79900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>88100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>95800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>104000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>111200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>87200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>106600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>98700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>90300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>59400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>73400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>48000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>56600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>48200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>63100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>41900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>50100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>36000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>34900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>39000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>35200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>30800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>25700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>21300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>32900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>37600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>42200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>27500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>24300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>26200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5473,26 +5607,26 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>15500</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>11600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>15000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>14600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>14200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10400</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -5550,8 +5684,8 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>24</v>
+      <c r="AE58" s="3">
+        <v>0</v>
       </c>
       <c r="AF58" s="3" t="s">
         <v>24</v>
@@ -5559,11 +5693,11 @@
       <c r="AG58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AH58" s="3">
-        <v>0</v>
+      <c r="AH58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AI58" s="3">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AJ58" s="3">
         <v>10000</v>
@@ -5571,257 +5705,266 @@
       <c r="AK58" s="3">
         <v>10000</v>
       </c>
+      <c r="AL58" s="3">
+        <v>10000</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>149100</v>
+      </c>
+      <c r="E59" s="3">
         <v>142300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>107100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>93100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>83500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>84700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>65100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>73200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>56900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>113400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>75400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>95300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>92500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>104300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>93900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>102900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>106000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>163700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>83500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>84000</v>
-      </c>
-      <c r="W59" s="3">
-        <v>71900</v>
       </c>
       <c r="X59" s="3">
         <v>71900</v>
       </c>
       <c r="Y59" s="3">
+        <v>71900</v>
+      </c>
+      <c r="Z59" s="3">
         <v>59100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>59000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>58600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>62400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>57000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>50400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>46500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>36600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>33100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>45400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>39000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>32300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>296600</v>
+      </c>
+      <c r="E60" s="3">
         <v>273500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>232800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>234400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>207600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>225700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>205300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>233300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>220200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>200600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>182000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>193900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>182800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>163700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>167300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>150800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>162700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>211900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>146600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>125900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>122000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>107900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>94100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>98000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>93800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>93200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>82800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>71700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>79300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>74300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>75300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>72800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>73400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>68500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>56200</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>652200</v>
+      </c>
+      <c r="E61" s="3">
         <v>652900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>660900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>656500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>685600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>693500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>642200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>578300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>582800</v>
-      </c>
-      <c r="L61" s="3">
-        <v>511500</v>
       </c>
       <c r="M61" s="3">
         <v>511500</v>
       </c>
       <c r="N61" s="3">
-        <v>451500</v>
+        <v>511500</v>
       </c>
       <c r="O61" s="3">
         <v>451500</v>
@@ -5830,29 +5973,29 @@
         <v>451500</v>
       </c>
       <c r="Q61" s="3">
-        <v>200000</v>
+        <v>451500</v>
       </c>
       <c r="R61" s="3">
         <v>200000</v>
       </c>
       <c r="S61" s="3">
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="T61" s="3">
         <v>160000</v>
       </c>
       <c r="U61" s="3">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>200000</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -5860,22 +6003,22 @@
         <v>0</v>
       </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>276500</v>
-      </c>
-      <c r="AB61" s="3">
-        <v>240000</v>
       </c>
       <c r="AC61" s="3">
         <v>240000</v>
       </c>
       <c r="AD61" s="3">
-        <v>195000</v>
+        <v>240000</v>
       </c>
       <c r="AE61" s="3">
         <v>195000</v>
       </c>
       <c r="AF61" s="3">
-        <v>0</v>
+        <v>195000</v>
       </c>
       <c r="AG61" s="3">
         <v>0</v>
@@ -5884,123 +6027,129 @@
         <v>0</v>
       </c>
       <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>176100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>180700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>180200</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E62" s="3">
         <v>9400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7900</v>
-      </c>
-      <c r="J62" s="3">
-        <v>8400</v>
       </c>
       <c r="K62" s="3">
         <v>8400</v>
       </c>
       <c r="L62" s="3">
+        <v>8400</v>
+      </c>
+      <c r="M62" s="3">
         <v>91800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>116600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>121800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>125100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>128500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>118300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>120200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>126700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>146700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>98700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>100000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>100200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>87700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>84500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>34200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>29700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>27400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>27600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>25900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>26800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>12300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>13000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>17500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>20500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>21300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6106,8 +6255,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6213,8 +6365,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6320,115 +6475,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>963300</v>
+      </c>
+      <c r="E66" s="3">
         <v>941200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>909100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>906100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>905400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>931800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>860000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>824700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>823000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>803900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>810100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>767200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>759400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>743700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>485600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>471000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>449300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>518500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>245300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>225900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>422200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>195600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>178600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>132200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>400000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>360600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>350400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>292600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>301200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>86600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>88300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>90300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>270000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>270600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>247600</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6466,8 +6627,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6573,8 +6735,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6680,8 +6845,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6787,8 +6955,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6894,115 +7065,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>165500</v>
+      </c>
+      <c r="E72" s="3">
         <v>184700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>202300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>219800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>230600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>275200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>320700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>357400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>365700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>360500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>371400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>385800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>368900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>364700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>367400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>374500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>356600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>340900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>328300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>312500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>285200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>261700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>246000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>226700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>213900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>199800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>187400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>180000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>169900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>166200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>157000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>139100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>130300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>123200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>118000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7108,8 +7285,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7215,8 +7395,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7322,115 +7505,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1451100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1460300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1459800</v>
-      </c>
-      <c r="F76" s="3">
-        <v>1472800</v>
       </c>
       <c r="G76" s="3">
         <v>1472800</v>
       </c>
       <c r="H76" s="3">
+        <v>1472800</v>
+      </c>
+      <c r="I76" s="3">
         <v>1504500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1540800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1566700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1560900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1544100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1538900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1537200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1500400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1487100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1479500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1484100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1454000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1430600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1407900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1384800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1349400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1317100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1295300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1284700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>812400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>796100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>776600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>771900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>755800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>749200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>734300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>725400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>711400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>484700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>474500</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7536,227 +7725,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45744</v>
+      </c>
+      <c r="E80" s="2">
         <v>45653</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45562</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45471</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45380</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45289</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45198</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44925</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44743</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44652</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44470</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44379</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44288</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44197</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44106</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44015</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43917</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43826</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-17500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-44600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-45600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-36700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-14300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>16900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>17900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>15600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>12700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>15800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>27200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>23600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>15700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>19200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>12800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>14100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>12400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>7500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>10100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>9100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>18000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>8800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>5200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7794,115 +7992,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E83" s="3">
         <v>9900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>10100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>9900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>11100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>13700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>27200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>23700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>23400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>24500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>24100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>21500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>20800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>20000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>13300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>13000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>12500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>11400</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>11600</v>
       </c>
       <c r="AA83" s="3">
         <v>11600</v>
       </c>
       <c r="AB83" s="3">
+        <v>11600</v>
+      </c>
+      <c r="AC83" s="3">
         <v>11700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>11500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>12000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>11400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>9600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>9300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>9100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>7900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8008,8 +8210,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8115,8 +8320,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8222,8 +8430,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8329,8 +8540,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8436,115 +8650,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E89" s="3">
         <v>85500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-14700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>71800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-17800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>45500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-39100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>12600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>35400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-66000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-19400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>27200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>23200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>23900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>22900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>28700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>30100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>32100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>24300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>26000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>26200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>25300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>20000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>25600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>8800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>8000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>9700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>24900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>14200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8582,115 +8802,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7900</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-8000</v>
       </c>
       <c r="I91" s="3">
         <v>-8000</v>
       </c>
       <c r="J91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-8800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-10000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-11000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-11500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-10900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-11300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-9600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-8800</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-7100</v>
       </c>
       <c r="AB91" s="3">
         <v>-7100</v>
       </c>
       <c r="AC91" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8796,8 +9020,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8903,115 +9130,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7900</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-8000</v>
       </c>
       <c r="I94" s="3">
         <v>-8000</v>
       </c>
       <c r="J94" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-8800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-251300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-78500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-71600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-255900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-11000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-11500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-11300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-106100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-54400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-43600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-183100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-10000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-46900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-11600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-46500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-6200</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9049,8 +9282,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9078,8 +9312,8 @@
       <c r="K96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9156,8 +9390,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9263,8 +9500,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9370,8 +9610,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9477,135 +9720,141 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>1500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-23500</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>41200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>65000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>2400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>59900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>253800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-7300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>43100</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>163200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-197600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>201600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-14600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>173900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>36000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>36300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>194800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-192100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>210800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-8500</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-300</v>
       </c>
       <c r="J101" s="3">
         <v>-300</v>
@@ -9614,10 +9863,10 @@
         <v>-300</v>
       </c>
       <c r="L101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M101" s="3">
         <v>300</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-300</v>
       </c>
       <c r="N101" s="3">
         <v>-300</v>
@@ -9626,38 +9875,38 @@
         <v>-300</v>
       </c>
       <c r="P101" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-400</v>
-      </c>
-      <c r="T101" s="3">
-        <v>400</v>
       </c>
       <c r="U101" s="3">
         <v>400</v>
       </c>
       <c r="V101" s="3">
+        <v>400</v>
+      </c>
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-300</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
         <v>0</v>
       </c>
@@ -9668,134 +9917,140 @@
         <v>0</v>
       </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>300</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
       <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>700</v>
-      </c>
-      <c r="AI101" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ101" s="3">
         <v>-100</v>
       </c>
       <c r="AK101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E102" s="3">
         <v>84400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-22400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>37900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-26000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>79300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>17800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-12500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>25000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-26000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-13500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>9400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-18000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-8100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-48800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-68400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>12300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-180300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>225100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>20700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-96600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>145400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>18600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>21000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>6300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>22300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>12200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>6000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-15600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-228600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>224100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-31100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-4400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MRCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MRCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>MRCY</t>
   </si>
@@ -656,488 +656,501 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45835</v>
+      </c>
+      <c r="E7" s="2">
         <v>45744</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45653</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45562</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45471</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45380</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45289</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45198</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44925</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44743</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44652</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44470</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44379</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44288</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44197</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44106</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44015</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43917</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43826</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43735</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>273100</v>
+      </c>
+      <c r="E8" s="3">
         <v>211400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>223100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>204400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>248600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>208300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>197500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>181000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>253200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>263500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>229600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>227600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>289700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>253100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>220400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>225000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>250800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>256900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>210700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>205600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>217400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>208000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>193900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>177300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>177000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>174600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>159100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>144100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>152900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>116300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>117900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>106100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>115600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>107300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>98000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>87600</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>188300</v>
+      </c>
+      <c r="E9" s="3">
         <v>154200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>162300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>152600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>175400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>167600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>165900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>130500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>185900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>173200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>148600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>149500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>170200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>153300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>133200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>136600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>148100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>151200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>122000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>117500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>120800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>114700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>105400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>98900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>97100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>100800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>88200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>82500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>84600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>63600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>63800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>55400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>61700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>56500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>50600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>48200</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>84800</v>
+      </c>
+      <c r="E10" s="3">
         <v>57100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>60800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>51800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>73200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>40600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>31500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>50500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>67400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>90300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>81000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>78100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>119500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>99800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>87200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>88400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>102700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>105700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>88700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>88100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>96600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>93300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>88500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>78400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>79900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>73800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>70900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>61600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>68300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>52700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>54100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>50700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>53900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>50800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>47400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>39400</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1176,118 +1189,122 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E12" s="3">
         <v>16000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>21400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>18400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>19400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>21600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>28500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>31900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>27600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>26500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>26900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>27800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>25400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>28300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>28900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>27700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>30200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>28100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>27400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>27000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>25000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>24700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>21900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>20300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>17400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>16200</v>
-      </c>
-      <c r="AD12" s="3">
-        <v>14900</v>
       </c>
       <c r="AE12" s="3">
         <v>14900</v>
       </c>
       <c r="AF12" s="3">
+        <v>14900</v>
+      </c>
+      <c r="AG12" s="3">
         <v>15000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>15200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>13700</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>13900</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>14200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>13200</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1396,228 +1413,237 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E14" s="3">
         <v>3000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>8000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>12100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>8900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>9100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>6500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>14400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>8000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>3000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>3400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>400</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>2400</v>
       </c>
       <c r="Z14" s="3">
         <v>2400</v>
       </c>
       <c r="AA14" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AB14" s="3">
         <v>900</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>100</v>
       </c>
       <c r="AC14" s="3">
         <v>100</v>
       </c>
       <c r="AD14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE14" s="3">
         <v>900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>2700</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>400</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>900</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>1100</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E15" s="3">
         <v>10200</v>
-      </c>
-      <c r="E15" s="3">
-        <v>11200</v>
       </c>
       <c r="F15" s="3">
         <v>11200</v>
       </c>
       <c r="G15" s="3">
+        <v>11200</v>
+      </c>
+      <c r="H15" s="3">
         <v>11300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>11500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>12300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>12500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>12800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>13500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>14600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>14500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>16100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>16000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>13700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>13100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>12700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>7600</v>
-      </c>
-      <c r="V15" s="3">
-        <v>7700</v>
       </c>
       <c r="W15" s="3">
         <v>7700</v>
       </c>
       <c r="X15" s="3">
+        <v>7700</v>
+      </c>
+      <c r="Y15" s="3">
         <v>7800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>8000</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>7000</v>
       </c>
       <c r="AA15" s="3">
         <v>7000</v>
       </c>
       <c r="AB15" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AC15" s="3">
         <v>6800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>6900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>7200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>7400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>7100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>5800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>5600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>5500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>4700</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>4900</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1653,228 +1679,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>248200</v>
+      </c>
+      <c r="E17" s="3">
         <v>223500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>235300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>215400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>249400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>243900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>251200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>210700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>258100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>257100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>237100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>234800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>262100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>243100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>220800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>230600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>228400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>235500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>192800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>187000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>191300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>181800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>173200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>160100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>156100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>152600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>139200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>130200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>134000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>109500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>107000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>95700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>102600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>95600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>89100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>83900</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-12100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-11000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-35600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-53700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-29700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>27600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>10000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>22400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>21400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>17900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>18600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>26100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>26200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>20700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>17200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>20900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>22000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>19900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>13900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>18900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>6800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>10900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>10400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>13000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>11700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>8900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1913,558 +1946,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1300</v>
       </c>
-      <c r="G20" s="3">
-        <v>-3000</v>
-      </c>
       <c r="H20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I20" s="3">
         <v>700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2800</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>100</v>
       </c>
       <c r="Z20" s="3">
         <v>100</v>
       </c>
       <c r="AA20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1100</v>
       </c>
-      <c r="G21" s="3">
-        <v>13400</v>
-      </c>
       <c r="H21" s="3">
+        <v>9400</v>
+      </c>
+      <c r="I21" s="3">
         <v>-24800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-40400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-18400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>18900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>20800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>12900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>48400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>32400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>22400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>14500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>42500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>41500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>30500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>31000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>40700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>41600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>33300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>28600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>26300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>33500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>30800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>24400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>30300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>18300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>20200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>18900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>22400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>20100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>16700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E22" s="3">
         <v>8100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>8400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>8900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>6700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>6600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1100</v>
-      </c>
-      <c r="R22" s="3">
-        <v>600</v>
       </c>
       <c r="S22" s="3">
         <v>600</v>
       </c>
       <c r="T22" s="3">
+        <v>600</v>
+      </c>
+      <c r="U22" s="3">
         <v>500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3" t="s">
+      <c r="W22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>100</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
       <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
         <v>2200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>100</v>
       </c>
-      <c r="AH22" s="3">
-        <v>0</v>
-      </c>
       <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>2000</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>1900</v>
       </c>
       <c r="AK22" s="3">
         <v>1900</v>
       </c>
       <c r="AL22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AM22" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-21800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-24300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-23100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-18600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-57200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-63700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-49700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-14800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-13100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-15400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>22500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>21100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>21000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>17100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>18000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>27000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>28900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>20800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>17200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>12600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>19500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>16900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>10600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>16600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>10500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>9600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>11300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>10200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>7000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-6700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-5600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-7800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-12600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-18100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-13000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-6600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-10400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>6500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-8400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>3200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2573,228 +2622,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-19200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-17600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-44600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-45600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-36700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-10900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-14300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>16900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>17900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>15600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>12700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>15800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>27200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>23600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>15700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>19200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>12800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>14100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>12400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>7500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>10100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>7800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>18000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>8800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>7000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>5200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-19200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-17600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-44600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-45600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-36700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-10900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-14300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>16900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>17900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>15600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>12700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>15800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>27200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>23600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>15700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>19200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>12800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>14100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>12400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>7500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>10100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>7800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>18000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>8800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>7000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>5200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2903,8 +2961,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2971,8 +3032,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>24</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>24</v>
@@ -2992,20 +3053,20 @@
       <c r="AE29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-400</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>1300</v>
       </c>
-      <c r="AH29" s="3" t="s">
+      <c r="AI29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>24</v>
+      <c r="AJ29" s="3">
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>24</v>
@@ -3013,8 +3074,11 @@
       <c r="AL29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3123,8 +3187,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3233,228 +3300,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1300</v>
       </c>
-      <c r="G32" s="3">
-        <v>3000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I32" s="3">
         <v>-700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2800</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-100</v>
       </c>
       <c r="Z32" s="3">
         <v>-100</v>
       </c>
       <c r="AA32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB32" s="3">
         <v>6100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-19200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-17600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-44600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-45600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-36700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-10900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-14300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>16900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>17900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>15600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>12700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>15800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>27200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>23600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>15700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>19200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>12800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>14100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>12400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>7500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>10100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>9100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>18000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>8800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>7000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>5200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3563,233 +3639,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-19200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-17600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-44600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-45600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-36700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-10900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-14300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>16900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>17900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>15600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>12700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>15800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>27200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>23600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>15700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>19200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>12800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>14100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>12400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>7500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>10100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>9100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>18000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>8800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>7000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>5200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45835</v>
+      </c>
+      <c r="E38" s="2">
         <v>45744</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45653</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45562</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45471</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45380</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45289</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45198</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44925</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44743</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44652</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44470</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44379</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44288</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44197</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44106</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44015</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43917</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43826</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43735</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3828,8 +3913,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3868,118 +3954,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>309100</v>
+      </c>
+      <c r="E41" s="3">
         <v>269800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>242600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>158100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>180500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>142600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>168600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>89400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>71600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>64400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>76900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>52000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>65700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>91700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>105200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>95800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>113800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>121900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>109100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>239100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>226800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>407100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>182000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>161300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>257900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>112500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>93900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>72900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>66500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>44200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>32000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>26100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>41600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>270200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>46200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>77300</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4088,236 +4178,245 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>388100</v>
+      </c>
+      <c r="E43" s="3">
         <v>374700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>383100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>422800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>415500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>417200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>433700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>480000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>507300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>502300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>479300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>494700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>447900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>367100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>320100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>301200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>291700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>264000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>240200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>207800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>210700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>214000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>193400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>177500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>176200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>170700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>168300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>153900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>143800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>141600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>123000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>121500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>113700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>96600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>96900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>85700</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>332900</v>
+      </c>
+      <c r="E44" s="3">
         <v>352700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>344400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>351100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>335300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>343000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>354200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>362900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>337200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>342800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>312000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>287600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>270300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>259600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>251300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>234400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>221600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>226800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>218400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>206000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>178100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>161900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>153600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>148500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>137100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>131700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>126400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>121200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>108600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>117100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>105900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>93300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>81100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>72100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>70100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>500</v>
+      </c>
+      <c r="E45" s="3">
         <v>3000</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>24</v>
@@ -4325,211 +4424,217 @@
       <c r="G45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45" s="3">
         <v>28000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5800</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M45" s="3">
         <v>3600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>28600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>44500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>31400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>36700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>32200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>30300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>15900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>14200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>78000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>23700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>19100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>12400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>16100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>15800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>10900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>10300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>10700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>16300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>12800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>10300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>8000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>11200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>9800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>9400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>11700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1058200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1019500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>990700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>954300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>953800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>951500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>983800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>954700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>937000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>937900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>896900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>878800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>815300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>755000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>708800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>661700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>643100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>626900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>645700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>676700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>634800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>795400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>545100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>503000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>582200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>425200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>399300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>364200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>331700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>313200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>268900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>252000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>246200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>448400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>224800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>232000</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4545,24 +4650,24 @@
       <c r="G47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" s="3">
         <v>3600</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="3">
         <v>3500</v>
       </c>
-      <c r="L47" s="3" t="s">
+      <c r="M47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -4638,100 +4743,103 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>153700</v>
+      </c>
+      <c r="E48" s="3">
         <v>162100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>168000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>163400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>171200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>177200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>180000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>178100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>182600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>183400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>181700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>189700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>193600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>194700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>199400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>196500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>194900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>194100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>204500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>156700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>148400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>139800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>122500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>117300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>60000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>55900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>53100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>50800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>51000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>51300</v>
-      </c>
-      <c r="AG48" s="3">
-        <v>51600</v>
       </c>
       <c r="AH48" s="3">
         <v>51600</v>
@@ -4740,126 +4848,132 @@
         <v>51600</v>
       </c>
       <c r="AJ48" s="3">
+        <v>51600</v>
+      </c>
+      <c r="AK48" s="3">
         <v>47400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>39400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>31400</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1148700</v>
+      </c>
+      <c r="E49" s="3">
         <v>1154100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1164200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1177400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1188600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1199900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1211400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1223600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1236100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1248700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1261500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1274900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1289400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1303200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1318400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1102500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1112500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1077300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1093600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>815300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>822800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>831400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>839200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>847400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>768300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>724300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>696300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>704200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>675300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>685700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>505500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>510700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>509900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>483700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>489100</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>456600</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4968,8 +5082,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5078,118 +5195,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E52" s="3">
         <v>6200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>13800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>6400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>6800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>9800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>8300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>8000</v>
-      </c>
-      <c r="AJ52" s="3">
-        <v>2000</v>
       </c>
       <c r="AK52" s="3">
         <v>2000</v>
       </c>
       <c r="AL52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AM52" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5298,118 +5421,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2434800</v>
+      </c>
+      <c r="E54" s="3">
         <v>2414400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2401500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2369000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2378900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2378200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2436300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2400800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2391400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2383900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2348000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2349000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2304400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2259800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2230800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1965100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1955100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1903300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1949200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1653200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1610700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1771600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1512600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1473900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1417000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1212400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1156600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1127000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1064500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1056900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>835800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>822600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>815700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>981400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>755300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>722200</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5448,8 +5577,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5488,123 +5618,127 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>79100</v>
+      </c>
+      <c r="E57" s="3">
         <v>73600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>64800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>74700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>81100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>79900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>88100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>95800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>104000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>111200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>87200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>106600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>98700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>90300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>59400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>73400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>48000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>56600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>48200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>63100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>41900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>50100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>36000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>34900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>39000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>35200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>30800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>25700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>21300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>32900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>37600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>42200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>27500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>24300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>26200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>11800</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -5613,23 +5747,23 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>11600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>15000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>14600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>14200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10400</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5687,8 +5821,8 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>24</v>
+      <c r="AF58" s="3">
+        <v>0</v>
       </c>
       <c r="AG58" s="3" t="s">
         <v>24</v>
@@ -5696,11 +5830,11 @@
       <c r="AH58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AI58" s="3">
-        <v>0</v>
+      <c r="AI58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AJ58" s="3">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AK58" s="3">
         <v>10000</v>
@@ -5708,266 +5842,275 @@
       <c r="AL58" s="3">
         <v>10000</v>
       </c>
+      <c r="AM58" s="3">
+        <v>10000</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>135400</v>
+      </c>
+      <c r="E59" s="3">
         <v>149100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>142300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>107100</v>
       </c>
-      <c r="G59" s="3">
-        <v>93100</v>
-      </c>
       <c r="H59" s="3">
+        <v>88500</v>
+      </c>
+      <c r="I59" s="3">
         <v>83500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>84700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>65100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>73200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>56900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>113400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>75400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>95300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>92500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>104300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>93900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>102900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>106000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>163700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>83500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>84000</v>
-      </c>
-      <c r="X59" s="3">
-        <v>71900</v>
       </c>
       <c r="Y59" s="3">
         <v>71900</v>
       </c>
       <c r="Z59" s="3">
+        <v>71900</v>
+      </c>
+      <c r="AA59" s="3">
         <v>59100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>59000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>58600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>62400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>57000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>50400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>46500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>36600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>33100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>45400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>39000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>32300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>300400</v>
+      </c>
+      <c r="E60" s="3">
         <v>296600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>273500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>232800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>234400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>207600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>225700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>205300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>233300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>220200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>200600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>182000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>193900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>182800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>163700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>167300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>150800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>162700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>211900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>146600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>125900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>122000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>107900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>94100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>98000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>93800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>93200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>82800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>71700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>79300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>74300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>75300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>72800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>73400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>68500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>56200</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>649600</v>
+      </c>
+      <c r="E61" s="3">
         <v>652200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>652900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>660900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>656500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>685600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>693500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>642200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>578300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>582800</v>
-      </c>
-      <c r="M61" s="3">
-        <v>511500</v>
       </c>
       <c r="N61" s="3">
         <v>511500</v>
       </c>
       <c r="O61" s="3">
-        <v>451500</v>
+        <v>511500</v>
       </c>
       <c r="P61" s="3">
         <v>451500</v>
@@ -5976,29 +6119,29 @@
         <v>451500</v>
       </c>
       <c r="R61" s="3">
-        <v>200000</v>
+        <v>451500</v>
       </c>
       <c r="S61" s="3">
         <v>200000</v>
       </c>
       <c r="T61" s="3">
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="U61" s="3">
         <v>160000</v>
       </c>
       <c r="V61" s="3">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>200000</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -6006,22 +6149,22 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>276500</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>240000</v>
       </c>
       <c r="AD61" s="3">
         <v>240000</v>
       </c>
       <c r="AE61" s="3">
-        <v>195000</v>
+        <v>240000</v>
       </c>
       <c r="AF61" s="3">
         <v>195000</v>
       </c>
       <c r="AG61" s="3">
-        <v>0</v>
+        <v>195000</v>
       </c>
       <c r="AH61" s="3">
         <v>0</v>
@@ -6030,126 +6173,132 @@
         <v>0</v>
       </c>
       <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
         <v>176100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>180700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>180200</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E62" s="3">
         <v>9000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7900</v>
-      </c>
-      <c r="K62" s="3">
-        <v>8400</v>
       </c>
       <c r="L62" s="3">
         <v>8400</v>
       </c>
       <c r="M62" s="3">
+        <v>8400</v>
+      </c>
+      <c r="N62" s="3">
         <v>91800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>116600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>121800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>125100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>128500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>118300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>120200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>126700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>146700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>98700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>100000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>100200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>87700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>84500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>34200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>29700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>27400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>27600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>25900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>26800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>12300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>13000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>17500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>20500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>21300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6258,8 +6407,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6368,8 +6520,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6478,118 +6633,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>961300</v>
+      </c>
+      <c r="E66" s="3">
         <v>963300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>941200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>909100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>906100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>905400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>931800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>860000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>824700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>823000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>803900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>810100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>767200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>759400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>743700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>485600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>471000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>449300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>518500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>245300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>225900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>422200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>195600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>178600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>132200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>400000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>360600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>350400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>292600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>301200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>86600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>88300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>90300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>270000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>270600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>247600</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6628,8 +6789,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6738,8 +6900,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6848,8 +7013,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6958,8 +7126,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7068,118 +7239,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>181900</v>
+      </c>
+      <c r="E72" s="3">
         <v>165500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>184700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>202300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>219800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>230600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>275200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>320700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>357400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>365700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>360500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>371400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>385800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>368900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>364700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>367400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>374500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>356600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>340900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>328300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>312500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>285200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>261700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>246000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>226700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>213900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>199800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>187400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>180000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>169900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>166200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>157000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>139100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>130300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>123200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>118000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7288,8 +7465,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7398,8 +7578,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7508,118 +7691,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1473500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1451100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1460300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1459800</v>
-      </c>
-      <c r="G76" s="3">
-        <v>1472800</v>
       </c>
       <c r="H76" s="3">
         <v>1472800</v>
       </c>
       <c r="I76" s="3">
+        <v>1472800</v>
+      </c>
+      <c r="J76" s="3">
         <v>1504500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1540800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1566700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1560900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1544100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1538900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1537200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1500400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1487100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1479500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1484100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1454000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1430600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1407900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1384800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1349400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1317100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1295300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1284700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>812400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>796100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>776600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>771900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>755800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>749200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>734300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>725400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>711400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>484700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>474500</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7728,233 +7917,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45835</v>
+      </c>
+      <c r="E80" s="2">
         <v>45744</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45653</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45562</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45471</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45380</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45289</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45198</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44925</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44743</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44652</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44470</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44379</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44288</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44197</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44106</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44015</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43917</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43826</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43735</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-19200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-17600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-44600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-45600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-36700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-10900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-14300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>16900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>17900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>15600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>12700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>15800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>27200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>23600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>15700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>19200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>12800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>14100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>12400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>7500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>10100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>9100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>18000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>8800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>7000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>5200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7993,118 +8191,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E83" s="3">
         <v>10200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>9900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>10100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>11100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>27200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>23700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>23400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>24500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>24100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>21500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>20800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>20000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>13300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>13000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>12700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>11400</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>11600</v>
       </c>
       <c r="AB83" s="3">
         <v>11600</v>
       </c>
       <c r="AC83" s="3">
+        <v>11600</v>
+      </c>
+      <c r="AD83" s="3">
         <v>11700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>11500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>12000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>11400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>9600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>9300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>9100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>8000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>7900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8213,8 +8415,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8323,8 +8528,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8433,8 +8641,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8543,8 +8754,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8653,118 +8867,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E89" s="3">
         <v>30000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>85500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-14700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>71800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-17800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>45500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-39100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>12600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>35400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-66000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-19400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>27200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>23200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>23900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>22900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>28700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>30100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>32100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>24300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>26000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>26200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>25300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>20000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>25600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>8800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>8000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>9700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>24900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>14200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8803,118 +9023,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7900</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-8000</v>
       </c>
       <c r="J91" s="3">
         <v>-8000</v>
       </c>
       <c r="K91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="L91" s="3">
         <v>-8800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-10900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-10000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-11000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-11500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-10900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-11300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-8800</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-7100</v>
       </c>
       <c r="AC91" s="3">
         <v>-7100</v>
       </c>
       <c r="AD91" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9023,8 +9247,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9133,118 +9360,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7900</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-8000</v>
       </c>
       <c r="J94" s="3">
         <v>-8000</v>
       </c>
       <c r="K94" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="L94" s="3">
         <v>-8800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-13100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-251300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-8600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-78500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-71600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-255900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-11000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-11500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-11300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-106100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-54400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-43600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-183100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-10000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-46900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-11600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-46500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-6200</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9283,8 +9516,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9315,8 +9549,8 @@
       <c r="L96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9393,8 +9627,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9503,8 +9740,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9613,8 +9853,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9723,141 +9966,147 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>1500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-23500</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>41200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>65000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>2400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>59900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>253800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-7300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>43100</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>163200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-197600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>201600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-14600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>173900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>36000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>36300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>194800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-192100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>210800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>1200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-8500</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>300</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-300</v>
       </c>
       <c r="K101" s="3">
         <v>-300</v>
@@ -9866,10 +10115,10 @@
         <v>-300</v>
       </c>
       <c r="M101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N101" s="3">
         <v>300</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-300</v>
       </c>
       <c r="O101" s="3">
         <v>-300</v>
@@ -9878,38 +10127,38 @@
         <v>-300</v>
       </c>
       <c r="Q101" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-400</v>
-      </c>
-      <c r="U101" s="3">
-        <v>400</v>
       </c>
       <c r="V101" s="3">
         <v>400</v>
       </c>
       <c r="W101" s="3">
+        <v>400</v>
+      </c>
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-300</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
         <v>0</v>
       </c>
@@ -9920,137 +10169,143 @@
         <v>0</v>
       </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>300</v>
       </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
       <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>700</v>
-      </c>
-      <c r="AJ101" s="3">
-        <v>-100</v>
       </c>
       <c r="AK101" s="3">
         <v>-100</v>
       </c>
       <c r="AL101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E102" s="3">
         <v>27300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>84400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-22400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>37900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-26000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>79300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>17800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-12500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>25000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-26000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>9400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-18000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-8100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-48800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-68400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>12300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-180300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>225100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>20700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-96600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>145400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>18600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>21000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>6300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>22300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>12200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>6000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-15600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-228600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>224100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-31100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-4400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MRCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MRCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>MRCY</t>
   </si>
@@ -656,514 +656,526 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46017</v>
+      </c>
+      <c r="E7" s="2">
         <v>45926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45835</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45744</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45653</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45562</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45471</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45380</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45289</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45198</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44925</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44743</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44652</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44470</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44379</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44288</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44197</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44106</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44015</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43917</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43826</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43735</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>232900</v>
+      </c>
+      <c r="E8" s="3">
         <v>225200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>273100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>211400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>223100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>204400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>248600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>208300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>197500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>181000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>253200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>263500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>229600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>227600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>289700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>253100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>220400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>225000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>250800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>256900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>210700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>205600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>217400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>208000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>193900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>177300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>177000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>174600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>159100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>144100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>152900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>116300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>117900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>106100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>115600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>107300</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>98000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>87600</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>172200</v>
+      </c>
+      <c r="E9" s="3">
         <v>162300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>188300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>154200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>162300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>152600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>175400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>167600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>165900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>130500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>185900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>173200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>148600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>149500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>170200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>153300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>133200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>136600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>148100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>151200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>122000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>117500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>120800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>114700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>105400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>98900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>97100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>100800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>88200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>82500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>84600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>63600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>63800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>55400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>61700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>56500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>50600</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>48200</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E10" s="3">
         <v>62900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>84800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>57100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>60800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>51800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>73200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>40600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>31500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>50500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>67400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>90300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>81000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>78100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>119500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>99800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>87200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>88400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>102700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>105700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>88700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>88100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>96600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>93300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>88500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>78400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>79900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>73800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>70900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>61600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>68300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>52700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>54100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>50700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>53900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>50800</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>47400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>39400</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1204,124 +1216,128 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E12" s="3">
         <v>13200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>11900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>16000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>21400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>18400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>19400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>21600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>28500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>31900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>27600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>26500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>26900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>27800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>24600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>25400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>28300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>28900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>27700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>30200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>28100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>27400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>27000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>25000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>24700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>21900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>20300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>17400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>16200</v>
-      </c>
-      <c r="AF12" s="3">
-        <v>14900</v>
       </c>
       <c r="AG12" s="3">
         <v>14900</v>
       </c>
       <c r="AH12" s="3">
+        <v>14900</v>
+      </c>
+      <c r="AI12" s="3">
         <v>15000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>15200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>13700</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>13900</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>14200</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>13200</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1436,240 +1452,249 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E14" s="3">
         <v>7300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>8000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>12100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>11000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>8900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>9100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>6500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>14400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>8000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>3000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>3400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>400</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>2400</v>
       </c>
       <c r="AB14" s="3">
         <v>2400</v>
       </c>
       <c r="AC14" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AD14" s="3">
         <v>900</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>100</v>
       </c>
       <c r="AE14" s="3">
         <v>100</v>
       </c>
       <c r="AF14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG14" s="3">
         <v>900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1600</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>2700</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>400</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>1200</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>900</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>1100</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>10300</v>
+        <v>9700</v>
       </c>
       <c r="E15" s="3">
         <v>10300</v>
       </c>
       <c r="F15" s="3">
+        <v>10300</v>
+      </c>
+      <c r="G15" s="3">
         <v>10200</v>
-      </c>
-      <c r="G15" s="3">
-        <v>11200</v>
       </c>
       <c r="H15" s="3">
         <v>11200</v>
       </c>
       <c r="I15" s="3">
+        <v>11200</v>
+      </c>
+      <c r="J15" s="3">
         <v>11300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>12500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>12600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>12800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>13500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>14600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>14500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>16100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>16000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>13700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>13100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>12700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>7600</v>
-      </c>
-      <c r="X15" s="3">
-        <v>7700</v>
       </c>
       <c r="Y15" s="3">
         <v>7700</v>
       </c>
       <c r="Z15" s="3">
+        <v>7700</v>
+      </c>
+      <c r="AA15" s="3">
         <v>7800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>8000</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>7000</v>
       </c>
       <c r="AC15" s="3">
         <v>7000</v>
       </c>
       <c r="AD15" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AE15" s="3">
         <v>6800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>6900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>7200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>7400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>7100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>5600</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>5500</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>4700</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>4900</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1707,240 +1732,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>239500</v>
+      </c>
+      <c r="E17" s="3">
         <v>226500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>248200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>223500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>235300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>215400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>249400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>243900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>251200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>210700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>258100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>257100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>237100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>234800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>262100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>243100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>220800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>230600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>228400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>235500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>192800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>187000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>191300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>181800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>173200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>160100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>156100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>152600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>139200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>130200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>134000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>109500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>107000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>95700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>102600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>95600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>89100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>83900</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>24900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-12100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-12200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-11000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-35600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-53700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-29700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>27600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>10000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>22400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>21400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>17900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>18600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>26100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>26200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>20700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>17200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>20900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>22000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>19900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>13900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>18900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>6800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>10900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>10400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>13000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>11700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>8900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1981,588 +2013,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E20" s="3">
         <v>2100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2800</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>100</v>
       </c>
       <c r="AB20" s="3">
         <v>100</v>
       </c>
       <c r="AC20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-6100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E21" s="3">
         <v>6900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>39000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-24800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-40400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-18400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>18900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>20800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>12900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>48400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>32400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>22400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>14500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>42500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>41500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>30500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>31000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>40700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>41600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>33300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>28600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>26300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>33500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>30800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>24400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>30300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>18300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>20200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>18900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>22400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>20100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>16700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E22" s="3">
         <v>7900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>8000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>8100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>8400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>8900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>4500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1100</v>
-      </c>
-      <c r="T22" s="3">
-        <v>600</v>
       </c>
       <c r="U22" s="3">
         <v>600</v>
       </c>
       <c r="V22" s="3">
+        <v>600</v>
+      </c>
+      <c r="W22" s="3">
         <v>500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>100</v>
       </c>
-      <c r="X22" s="3" t="s">
+      <c r="Y22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>100</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
       <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
         <v>2200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>2300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>100</v>
       </c>
-      <c r="AJ22" s="3">
-        <v>0</v>
-      </c>
       <c r="AK22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="3">
         <v>2000</v>
-      </c>
-      <c r="AL22" s="3">
-        <v>1900</v>
       </c>
       <c r="AM22" s="3">
         <v>1900</v>
       </c>
       <c r="AN22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AO22" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-16500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>18800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-21800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-24300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-23100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-18600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-57200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-63700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-49700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-13100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-15400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>22500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-7600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>21100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>21000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>17100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>18000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>27000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>28900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>20800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>17200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>12600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>19500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>16900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>10600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>16600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>5900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>10500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>9600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>11300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>10200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>7000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-4000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-6700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-5600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-7800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-12600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-18100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-13000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-6600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-10400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>6500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>2600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-8400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>2500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>3200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>1800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2677,240 +2725,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>16400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-19200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-17500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-44600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-45600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-36700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>16900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-7100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>17900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>15600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>12700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>15800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>27200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>23600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>15700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>19200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>12800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>14100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>12400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>7500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>10100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>7800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>18000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>8800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>7000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>5200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>16400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-17500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-44600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-45600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-36700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>16900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>17900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>15600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>12700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>15800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>27200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>23600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>15700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>19200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>12800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>14100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>12400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>7500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>10100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>7800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>18000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>8800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>7000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>5200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3025,8 +3082,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3099,8 +3159,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>24</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>24</v>
@@ -3120,20 +3180,20 @@
       <c r="AG29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AH29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI29" s="3">
         <v>-400</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ29" s="3" t="s">
+      <c r="AK29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AK29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
+      <c r="AL29" s="3">
+        <v>0</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
@@ -3141,8 +3201,11 @@
       <c r="AN29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3257,8 +3320,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3373,240 +3439,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2800</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-100</v>
       </c>
       <c r="AB32" s="3">
         <v>-100</v>
       </c>
       <c r="AC32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD32" s="3">
         <v>6100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>16400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-17500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-10800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-44600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-45600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-36700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-10900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>16900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>17900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>15600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>12700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>15800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>27200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>23600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>15700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>19200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>12800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>14100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>12400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>7500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>10100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>9100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>18000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>8800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>7000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>5200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3721,245 +3796,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>16400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-17500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-10800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-44600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-45600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-36700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-10900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>16900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>17900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>15600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>12700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>15800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>27200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>23600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>15700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>19200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>12800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>14100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>12400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>7500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>10100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>9100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>18000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>8800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>7000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>5200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46017</v>
+      </c>
+      <c r="E38" s="2">
         <v>45926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45835</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45744</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45653</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45562</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45471</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45380</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45289</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45198</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44925</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44743</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44652</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44470</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44379</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44288</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44197</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44106</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44015</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43917</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43826</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43735</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4000,8 +4084,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4042,124 +4127,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>335000</v>
+      </c>
+      <c r="E41" s="3">
         <v>304700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>309100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>269800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>242600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>158100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>180500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>142600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>168600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>89400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>71600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>64400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>76900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>52000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>65700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>91700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>105200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>95800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>113800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>121900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>109100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>239100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>226800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>407100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>182000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>161300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>257900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>112500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>93900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>72900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>66500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>44200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>32000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>26100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>41600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>270200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>46200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>77300</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4274,254 +4363,263 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>379800</v>
+      </c>
+      <c r="E43" s="3">
         <v>367500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>388100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>374700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>383100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>422800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>415500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>417200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>433700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>480000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>507300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>502300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>479300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>494700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>447900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>367100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>320100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>301200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>291700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>264000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>240200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>207800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>210700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>214000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>193400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>177500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>176200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>170700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>168300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>153900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>143800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>141600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>123000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>121500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>113700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>96600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>96900</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>85700</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>349600</v>
+      </c>
+      <c r="E44" s="3">
         <v>340200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>332900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>352700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>344400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>351100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>335300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>343000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>354200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>362900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>337200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>342800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>312000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>287600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>270300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>259600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>251300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>234400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>221600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>226800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>218400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>206000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>178100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>161900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>153600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>148500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>137100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>131700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>126400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>121200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>108600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>117100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>105900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>93300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>81100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>72100</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>70100</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1400</v>
+        <v>33700</v>
       </c>
       <c r="E45" s="3">
+        <v>33900</v>
+      </c>
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3000</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>24</v>
@@ -4529,217 +4627,223 @@
       <c r="I45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K45" s="3">
         <v>28000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5800</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O45" s="3">
         <v>3600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>28600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>44500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>31400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>36700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>32200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>30300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>15900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>14200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>78000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>23700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>19100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>12400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>16100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>15800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>10900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>10300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>10700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>16300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>12800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>10300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>11200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>9800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>9400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>11700</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1132200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1084600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1058200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1019500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>990700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>954300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>953800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>951500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>983800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>954700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>937000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>937900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>896900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>878800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>815300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>755000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>708800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>661700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>643100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>626900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>645700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>676700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>634800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>795400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>545100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>503000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>582200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>425200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>399300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>364200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>331700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>313200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>268900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>252000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>246200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>448400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>224800</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>232000</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4761,24 +4865,24 @@
       <c r="I47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K47" s="3">
         <v>3600</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N47" s="3">
         <v>3500</v>
       </c>
-      <c r="N47" s="3" t="s">
+      <c r="O47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -4854,106 +4958,109 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>154000</v>
+      </c>
+      <c r="E48" s="3">
         <v>156500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>153700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>162100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>168000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>163400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>171200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>177200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>180000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>178100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>182600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>183400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>181700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>189700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>193600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>194700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>199400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>196500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>194900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>194100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>204500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>156700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>148400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>139800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>122500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>117300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>60000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>55900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>53100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>50800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>51000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>51300</v>
-      </c>
-      <c r="AI48" s="3">
-        <v>51600</v>
       </c>
       <c r="AJ48" s="3">
         <v>51600</v>
@@ -4962,132 +5069,138 @@
         <v>51600</v>
       </c>
       <c r="AL48" s="3">
+        <v>51600</v>
+      </c>
+      <c r="AM48" s="3">
         <v>47400</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>39400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>31400</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1131300</v>
+      </c>
+      <c r="E49" s="3">
         <v>1138500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1148700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1154100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1164200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1177400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1188600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1199900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1211400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1223600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1236100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1248700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1261500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1274900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1289400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1303200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1318400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1102500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1112500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1077300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1093600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>815300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>822800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>831400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>839200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>847400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>768300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>724300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>696300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>704200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>675300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>685700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>505500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>510700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>509900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>483700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>489100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>456600</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5202,8 +5315,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5318,124 +5434,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E52" s="3">
         <v>5100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>13800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>7800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>6400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>6800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>9800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>8300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>8000</v>
-      </c>
-      <c r="AL52" s="3">
-        <v>2000</v>
       </c>
       <c r="AM52" s="3">
         <v>2000</v>
       </c>
       <c r="AN52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AO52" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5550,124 +5672,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2502100</v>
+      </c>
+      <c r="E54" s="3">
         <v>2457600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2434800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2414400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2401500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2369000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2378900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2378200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2436300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2400800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2391400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2383900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2348000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2349000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2304400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2259800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2230800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1965100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1955100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1903300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1949200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1653200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1610700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1771600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1512600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1473900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1417000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1212400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1156600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1127000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1064500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1056900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>835800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>822600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>815700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>981400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>755300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>722200</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5708,8 +5836,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5750,136 +5879,140 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>106200</v>
+      </c>
+      <c r="E57" s="3">
         <v>97800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>79100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>73600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>64800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>74700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>81100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>79900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>88100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>95800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>104000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>111200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>87200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>106600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>98700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>90300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>59400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>73400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>48000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>56600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>48200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>63100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>41900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>50100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>36000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>34900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>39000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>35200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>30800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>25700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>21300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>32900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>37600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>42200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>27500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>24300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>26200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>32300</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>11800</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -5887,23 +6020,23 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>11600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>15000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>14600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>14200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10400</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -5961,8 +6094,8 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>24</v>
+      <c r="AH58" s="3">
+        <v>0</v>
       </c>
       <c r="AI58" s="3" t="s">
         <v>24</v>
@@ -5970,11 +6103,11 @@
       <c r="AJ58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AK58" s="3">
-        <v>0</v>
+      <c r="AK58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AL58" s="3">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AM58" s="3">
         <v>10000</v>
@@ -5982,284 +6115,293 @@
       <c r="AN58" s="3">
         <v>10000</v>
       </c>
+      <c r="AO58" s="3">
+        <v>10000</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>129800</v>
+        <v>144100</v>
       </c>
       <c r="E59" s="3">
+        <v>162300</v>
+      </c>
+      <c r="F59" s="3">
         <v>135400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>149100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>142300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>107100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>88500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>83500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>84700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>65100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>73200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>56900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>113400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>75400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>95300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>92500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>104300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>93900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>102900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>106000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>163700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>83500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>84000</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>71900</v>
       </c>
       <c r="AA59" s="3">
         <v>71900</v>
       </c>
       <c r="AB59" s="3">
+        <v>71900</v>
+      </c>
+      <c r="AC59" s="3">
         <v>59100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>59000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>58600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>62400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>57000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>50400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>46500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>36600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>33100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>45400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>39000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>32300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>383000</v>
+      </c>
+      <c r="E60" s="3">
         <v>322200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>300400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>296600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>273500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>232800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>234400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>207600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>225700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>205300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>233300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>220200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>200600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>182000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>193900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>182800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>163700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>167300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>150800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>162700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>211900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>146600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>125900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>122000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>107900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>94100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>98000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>93800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>93200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>82800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>71700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>79300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>74300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>75300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>72800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>73400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>68500</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>56200</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>646900</v>
+      </c>
+      <c r="E61" s="3">
         <v>649900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>649600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>652200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>652900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>660900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>656500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>685600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>693500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>642200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>578300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>582800</v>
-      </c>
-      <c r="O61" s="3">
-        <v>511500</v>
       </c>
       <c r="P61" s="3">
         <v>511500</v>
       </c>
       <c r="Q61" s="3">
-        <v>451500</v>
+        <v>511500</v>
       </c>
       <c r="R61" s="3">
         <v>451500</v>
@@ -6268,29 +6410,29 @@
         <v>451500</v>
       </c>
       <c r="T61" s="3">
-        <v>200000</v>
+        <v>451500</v>
       </c>
       <c r="U61" s="3">
         <v>200000</v>
       </c>
       <c r="V61" s="3">
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="W61" s="3">
         <v>160000</v>
       </c>
       <c r="X61" s="3">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>200000</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -6298,22 +6440,22 @@
         <v>0</v>
       </c>
       <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>276500</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>240000</v>
       </c>
       <c r="AF61" s="3">
         <v>240000</v>
       </c>
       <c r="AG61" s="3">
-        <v>195000</v>
+        <v>240000</v>
       </c>
       <c r="AH61" s="3">
         <v>195000</v>
       </c>
       <c r="AI61" s="3">
-        <v>0</v>
+        <v>195000</v>
       </c>
       <c r="AJ61" s="3">
         <v>0</v>
@@ -6322,132 +6464,138 @@
         <v>0</v>
       </c>
       <c r="AL61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM61" s="3">
         <v>176100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>180700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>180200</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E62" s="3">
         <v>4800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7900</v>
-      </c>
-      <c r="M62" s="3">
-        <v>8400</v>
       </c>
       <c r="N62" s="3">
         <v>8400</v>
       </c>
       <c r="O62" s="3">
+        <v>8400</v>
+      </c>
+      <c r="P62" s="3">
         <v>91800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>116600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>121800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>125100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>128500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>118300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>120200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>126700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>146700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>98700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>100000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>100200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>87700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>84500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>34200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>29700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>27400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>27600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>25900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>26800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>12300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>13000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>17500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>20500</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>21300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6562,8 +6710,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6678,8 +6829,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6794,124 +6948,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1042100</v>
+      </c>
+      <c r="E66" s="3">
         <v>982600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>961300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>963300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>941200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>909100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>906100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>905400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>931800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>860000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>824700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>823000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>803900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>810100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>767200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>759400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>743700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>485600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>471000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>449300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>518500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>245300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>225900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>422200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>195600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>178600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>132200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>400000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>360600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>350400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>292600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>301200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>86600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>88300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>90300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>270000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>270600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>247600</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6952,8 +7112,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7068,8 +7229,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7184,8 +7348,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7300,8 +7467,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7416,124 +7586,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>154300</v>
+      </c>
+      <c r="E72" s="3">
         <v>169400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>181900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>165500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>184700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>202300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>219800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>230600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>275200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>320700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>357400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>365700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>360500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>371400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>385800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>368900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>364700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>367400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>374500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>356600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>340900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>328300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>312500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>285200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>261700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>246000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>226700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>213900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>199800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>187400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>180000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>169900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>166200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>157000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>139100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>130300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>123200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>118000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7648,8 +7824,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7764,8 +7943,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7880,124 +8062,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1460000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1475000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1473500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1451100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1460300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1459800</v>
-      </c>
-      <c r="I76" s="3">
-        <v>1472800</v>
       </c>
       <c r="J76" s="3">
         <v>1472800</v>
       </c>
       <c r="K76" s="3">
+        <v>1472800</v>
+      </c>
+      <c r="L76" s="3">
         <v>1504500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1540800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1566700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1560900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1544100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1538900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1537200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1500400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1487100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1479500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1484100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1454000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1430600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1407900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1384800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1349400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1317100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1295300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1284700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>812400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>796100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>776600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>771900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>755800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>749200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>734300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>725400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>711400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>484700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>474500</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8112,245 +8300,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46017</v>
+      </c>
+      <c r="E80" s="2">
         <v>45926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45835</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45744</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45653</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45562</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45471</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45380</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45289</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45198</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44925</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44743</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44652</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44470</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44379</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44288</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44197</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44106</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44015</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43917</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43826</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43735</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>16400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-17500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-10800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-44600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-45600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-36700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-10900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>16900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>17900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>15600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>12700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>15800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>27200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>23600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>15700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>19200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>12800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>14100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>12400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>7500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>10100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>9100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>18000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>8800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>7000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>5200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8391,124 +8588,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E83" s="3">
         <v>10000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>10100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>10200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>10100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>11100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>9100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>8900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>27200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>23700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>23400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>24500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>24100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>21500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>20800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>20000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>13300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>13000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>12500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>11400</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>11600</v>
       </c>
       <c r="AD83" s="3">
         <v>11600</v>
       </c>
       <c r="AE83" s="3">
+        <v>11600</v>
+      </c>
+      <c r="AF83" s="3">
         <v>11700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>11500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>12000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>11400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>9600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>9300</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>9100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>8000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>7900</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8623,8 +8824,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8739,8 +8943,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8855,8 +9062,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8971,8 +9181,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9087,124 +9300,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>51600</v>
+      </c>
+      <c r="E89" s="3">
         <v>2200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>38100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>30000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>85500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-14700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>71800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-17800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>45500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-39100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>12600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>35400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-66000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-19400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>6800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>27200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>23200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>23900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>22900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>28700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>30100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>32100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>24300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>26000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>26200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>25300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>20000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>25600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>8800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>8000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>9700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>24900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>14200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9245,124 +9464,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7900</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-8000</v>
       </c>
       <c r="L91" s="3">
         <v>-8000</v>
       </c>
       <c r="M91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="N91" s="3">
         <v>-8800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-9400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-8000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-10000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-13800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-11500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-10900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-11300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-8800</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-7100</v>
       </c>
       <c r="AE91" s="3">
         <v>-7100</v>
       </c>
       <c r="AF91" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9477,8 +9700,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9593,124 +9819,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7900</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-8000</v>
       </c>
       <c r="L94" s="3">
         <v>-8000</v>
       </c>
       <c r="M94" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="N94" s="3">
         <v>-8800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-13100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-251300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-8600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-78500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-71600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-255900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-11500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-6600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-11300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-106100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-54400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-43600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-183100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-10000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-46900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-11600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-46500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-6200</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9751,8 +9983,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9789,8 +10022,8 @@
       <c r="N96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9867,8 +10100,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9983,8 +10219,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10099,8 +10338,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10215,153 +10457,159 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="D100" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2200</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>1500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-23500</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>41200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>65000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>2400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>59900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>253800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-7300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>43100</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>163200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-197600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>201600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-14600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>173900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>36000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>36300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>194800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-192100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>210800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>1200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-8500</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-300</v>
       </c>
       <c r="M101" s="3">
         <v>-300</v>
@@ -10370,10 +10618,10 @@
         <v>-300</v>
       </c>
       <c r="O101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P101" s="3">
         <v>300</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-300</v>
       </c>
       <c r="Q101" s="3">
         <v>-300</v>
@@ -10382,38 +10630,38 @@
         <v>-300</v>
       </c>
       <c r="S101" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-400</v>
-      </c>
-      <c r="W101" s="3">
-        <v>400</v>
       </c>
       <c r="X101" s="3">
         <v>400</v>
       </c>
       <c r="Y101" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-300</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
         <v>0</v>
       </c>
@@ -10424,143 +10672,149 @@
         <v>0</v>
       </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>300</v>
       </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
-      </c>
       <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3">
         <v>700</v>
-      </c>
-      <c r="AL101" s="3">
-        <v>-100</v>
       </c>
       <c r="AM101" s="3">
         <v>-100</v>
       </c>
       <c r="AN101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AO101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>39300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>27300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>84400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-22400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>37900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-26000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>79300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>17800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>25000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-26000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-13500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>9400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-18000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-8100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-48800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-68400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>12300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-180300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>225100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>20700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-96600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>145400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>18600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>21000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>6300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>22300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>12200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-15600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-228600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>224100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-31100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-4400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MRCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MRCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>MRCY</t>
   </si>
@@ -656,526 +656,539 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46108</v>
+      </c>
+      <c r="E7" s="2">
         <v>46017</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45835</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45744</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45653</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45562</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45471</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45380</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45289</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45198</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44925</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44743</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44652</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44470</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44379</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44288</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44197</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44106</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44015</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43917</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43826</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43735</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>235800</v>
+      </c>
+      <c r="E8" s="3">
         <v>232900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>225200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>273100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>211400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>223100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>204400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>248600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>208300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>197500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>181000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>253200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>263500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>229600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>227600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>289700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>253100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>220400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>225000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>250800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>256900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>210700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>205600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>217400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>208000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>193900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>177300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>177000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>174600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>159100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>144100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>152900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>116300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>117900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>106100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>115600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>107300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>98000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>87600</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>166700</v>
+      </c>
+      <c r="E9" s="3">
         <v>172200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>162300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>188300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>154200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>162300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>152600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>175400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>167600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>165900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>130500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>185900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>173200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>148600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>149500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>170200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>153300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>133200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>136600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>148100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>151200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>122000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>117500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>120800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>114700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>105400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>98900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>97100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>100800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>88200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>82500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>84600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>63600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>63800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>55400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>61700</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>56500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>50600</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>48200</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>69100</v>
+      </c>
+      <c r="E10" s="3">
         <v>60600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>62900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>84800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>57100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>60800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>51800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>73200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>40600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>31500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>50500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>67400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>90300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>81000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>78100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>119500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>99800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>87200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>88400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>102700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>105700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>88700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>88100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>96600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>93300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>88500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>78400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>79900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>73800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>70900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>61600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>68300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>52700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>54100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>50700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>53900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>50800</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>47400</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>39400</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1217,127 +1230,131 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E12" s="3">
         <v>15400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>13200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>11900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>16000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>21400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>18400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>19400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>21600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>28500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>31900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>27600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>26500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>26900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>27800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>24600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>25400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>28300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>28900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>27700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>30200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>28100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>27400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>27000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>25000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>24700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>21900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>20300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>17400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>16200</v>
-      </c>
-      <c r="AG12" s="3">
-        <v>14900</v>
       </c>
       <c r="AH12" s="3">
         <v>14900</v>
       </c>
       <c r="AI12" s="3">
+        <v>14900</v>
+      </c>
+      <c r="AJ12" s="3">
         <v>15000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>15200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>13700</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>13900</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>14200</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>13200</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1455,246 +1472,255 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F14" s="3">
+        <v>7300</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H14" s="3">
+        <v>8000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J14" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K14" s="3">
+        <v>8000</v>
+      </c>
+      <c r="L14" s="3">
+        <v>12100</v>
+      </c>
+      <c r="M14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N14" s="3">
+        <v>11000</v>
+      </c>
+      <c r="O14" s="3">
+        <v>2800</v>
+      </c>
+      <c r="P14" s="3">
+        <v>4800</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R14" s="3">
+        <v>4000</v>
+      </c>
+      <c r="S14" s="3">
+        <v>8900</v>
+      </c>
+      <c r="T14" s="3">
+        <v>9100</v>
+      </c>
+      <c r="U14" s="3">
         <v>6500</v>
       </c>
-      <c r="E14" s="3">
-        <v>7300</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="V14" s="3">
+        <v>14400</v>
+      </c>
+      <c r="W14" s="3">
+        <v>8000</v>
+      </c>
+      <c r="X14" s="3">
         <v>3000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="Y14" s="3">
+        <v>3400</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AA14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
-        <v>2400</v>
-      </c>
-      <c r="J14" s="3">
-        <v>8000</v>
-      </c>
-      <c r="K14" s="3">
-        <v>12100</v>
-      </c>
-      <c r="L14" s="3">
-        <v>1600</v>
-      </c>
-      <c r="M14" s="3">
-        <v>11000</v>
-      </c>
-      <c r="N14" s="3">
-        <v>2800</v>
-      </c>
-      <c r="O14" s="3">
-        <v>4800</v>
-      </c>
-      <c r="P14" s="3">
-        <v>3000</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>4000</v>
-      </c>
-      <c r="R14" s="3">
-        <v>8900</v>
-      </c>
-      <c r="S14" s="3">
-        <v>9100</v>
-      </c>
-      <c r="T14" s="3">
-        <v>6500</v>
-      </c>
-      <c r="U14" s="3">
-        <v>14400</v>
-      </c>
-      <c r="V14" s="3">
-        <v>8000</v>
-      </c>
-      <c r="W14" s="3">
-        <v>3000</v>
-      </c>
-      <c r="X14" s="3">
-        <v>3400</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>1500</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>300</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>400</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>2400</v>
       </c>
       <c r="AC14" s="3">
         <v>2400</v>
       </c>
       <c r="AD14" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AE14" s="3">
         <v>900</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>100</v>
       </c>
       <c r="AF14" s="3">
         <v>100</v>
       </c>
       <c r="AG14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH14" s="3">
         <v>900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>2700</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>1000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>400</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>1200</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>900</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>1100</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E15" s="3">
         <v>9700</v>
-      </c>
-      <c r="E15" s="3">
-        <v>10300</v>
       </c>
       <c r="F15" s="3">
         <v>10300</v>
       </c>
       <c r="G15" s="3">
+        <v>10300</v>
+      </c>
+      <c r="H15" s="3">
         <v>10200</v>
-      </c>
-      <c r="H15" s="3">
-        <v>11200</v>
       </c>
       <c r="I15" s="3">
         <v>11200</v>
       </c>
       <c r="J15" s="3">
+        <v>11200</v>
+      </c>
+      <c r="K15" s="3">
         <v>11300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>11500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>12300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>12500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>12600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>12800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>13500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>14600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>14500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>16100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>16000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>13700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>13100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>12700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>7600</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>7700</v>
       </c>
       <c r="Z15" s="3">
         <v>7700</v>
       </c>
       <c r="AA15" s="3">
+        <v>7700</v>
+      </c>
+      <c r="AB15" s="3">
         <v>7800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>8000</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>7000</v>
       </c>
       <c r="AD15" s="3">
         <v>7000</v>
       </c>
       <c r="AE15" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AF15" s="3">
         <v>6800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>6900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>7200</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>7400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>7100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>5800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>5600</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>5500</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>4700</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>4900</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1733,246 +1759,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>239500</v>
+        <v>228300</v>
       </c>
       <c r="E17" s="3">
+        <v>236500</v>
+      </c>
+      <c r="F17" s="3">
         <v>226500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>248200</v>
       </c>
-      <c r="G17" s="3">
-        <v>223500</v>
-      </c>
       <c r="H17" s="3">
-        <v>235300</v>
+        <v>218500</v>
       </c>
       <c r="I17" s="3">
+        <v>233300</v>
+      </c>
+      <c r="J17" s="3">
         <v>215400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>249400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>243900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>251200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>210700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>258100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>257100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>237100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>234800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>262100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>243100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>220800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>230600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>228400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>235500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>192800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>187000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>191300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>181800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>173200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>160100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>156100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>152600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>139200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>130200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>134000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>109500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>107000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>95700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>102600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>95600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>89100</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>83900</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-6600</v>
+        <v>7500</v>
       </c>
       <c r="E18" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>24900</v>
       </c>
-      <c r="G18" s="3">
-        <v>-12100</v>
-      </c>
       <c r="H18" s="3">
-        <v>-12200</v>
+        <v>-7100</v>
       </c>
       <c r="I18" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="J18" s="3">
         <v>-11000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-35600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-53700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-29700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-7200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>27600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>22400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>21400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>17900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>18600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>26100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>26200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>20700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>17200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>20900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>22000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>19900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>13900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>18900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>10900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>10400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>13000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>11700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>8900</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2014,603 +2047,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-3300</v>
+        <v>4400</v>
       </c>
       <c r="E20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F20" s="3">
         <v>2100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3800</v>
       </c>
-      <c r="G20" s="3">
-        <v>-100</v>
-      </c>
       <c r="H20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I20" s="3">
         <v>2700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2800</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>100</v>
       </c>
       <c r="AC20" s="3">
         <v>100</v>
       </c>
       <c r="AD20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>300</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>400</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-100</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>6500</v>
+        <v>12600</v>
       </c>
       <c r="E21" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F21" s="3">
         <v>6900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>39000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-1800</v>
-      </c>
       <c r="H21" s="3">
-        <v>-3700</v>
+        <v>4100</v>
       </c>
       <c r="I21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="J21" s="3">
         <v>-1100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-24800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-40400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-18400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>18900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>20800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>12900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>48400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>32400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>22400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>14500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>42500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>41500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>30500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>31000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>40700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>41600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>33300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>28600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>26300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>33500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>30800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>24400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>30300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>18300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>20200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>18900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>22400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>20100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>16700</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E22" s="3">
         <v>7800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>8000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>8100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>8400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>9300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>4500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1100</v>
-      </c>
-      <c r="U22" s="3">
-        <v>600</v>
       </c>
       <c r="V22" s="3">
         <v>600</v>
       </c>
       <c r="W22" s="3">
+        <v>600</v>
+      </c>
+      <c r="X22" s="3">
         <v>500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>100</v>
       </c>
-      <c r="Y22" s="3" t="s">
+      <c r="Z22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>100</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
       <c r="AC22" s="3">
         <v>0</v>
       </c>
       <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
         <v>2200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>2200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>2300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>100</v>
       </c>
-      <c r="AK22" s="3">
-        <v>0</v>
-      </c>
       <c r="AL22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="3">
         <v>2000</v>
-      </c>
-      <c r="AM22" s="3">
-        <v>1900</v>
       </c>
       <c r="AN22" s="3">
         <v>1900</v>
       </c>
       <c r="AO22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AP22" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-17500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>18800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-21800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-24300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-23100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-18600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-57200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-63700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-49700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-14800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-15400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>22500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-7600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>21100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>21000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>17100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>18000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>27000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>28900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>20800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>17200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>12600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>19500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>16900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>10600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>16600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>5900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>10500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>9600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>11300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>10200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>7000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-4000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-6700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-5600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-7800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-12600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-18100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-13000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-6600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-10400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>5400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>4500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>6500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>2600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-8400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>2500</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>3200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1800</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2728,246 +2777,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-15100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>16400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-19200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-17600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-17500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-44600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-45600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-36700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-8200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-14300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>16900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-7100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>17900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>15600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>12700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>15800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>27200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>23600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>15700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>19200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>12800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>14100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>12400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>7500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>10100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>4100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>7800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>18000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>8800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>7000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>5200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-15100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>16400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-19200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-17600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-17500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-44600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-45600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-36700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-8200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-14300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>16900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>17900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>15600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>12700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>15800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>27200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>23600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>15700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>19200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>12800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>14100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>12400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>7500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>10100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>4100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>7800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>18000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>8800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>7000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>5200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3085,8 +3143,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3162,8 +3223,8 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>24</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>24</v>
@@ -3183,20 +3244,20 @@
       <c r="AH29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>1300</v>
       </c>
-      <c r="AK29" s="3" t="s">
+      <c r="AL29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AL29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM29" s="3" t="s">
-        <v>24</v>
+      <c r="AM29" s="3">
+        <v>0</v>
       </c>
       <c r="AN29" s="3" t="s">
         <v>24</v>
@@ -3204,8 +3265,11 @@
       <c r="AO29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3323,8 +3387,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3442,246 +3509,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>3300</v>
+        <v>-4400</v>
       </c>
       <c r="E32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3800</v>
       </c>
-      <c r="G32" s="3">
-        <v>100</v>
-      </c>
       <c r="H32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-2700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2800</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-100</v>
       </c>
       <c r="AC32" s="3">
         <v>-100</v>
       </c>
       <c r="AD32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE32" s="3">
         <v>6100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-300</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-400</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>100</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-15100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>16400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-19200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-17600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-17500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-44600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-45600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-36700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-14300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>16900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>17900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>15600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>12700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>15800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>27200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>23600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>15700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>19200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>12800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>14100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>12400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>7500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>10100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>9100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>18000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>8800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>7000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>5200</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3799,251 +3875,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-15100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>16400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-19200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-17600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-17500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-44600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-45600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-36700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-14300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>16900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>17900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>15600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>12700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>15800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>27200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>23600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>15700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>19200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>12800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>14100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>12400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>7500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>10100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>9100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>18000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>8800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>7000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>5200</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46108</v>
+      </c>
+      <c r="E38" s="2">
         <v>46017</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45835</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45744</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45653</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45562</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45471</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45380</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45289</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45198</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44925</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44743</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44652</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44470</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44379</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44288</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44197</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44106</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44015</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43917</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43826</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43735</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4085,8 +4170,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4128,127 +4214,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>331800</v>
+      </c>
+      <c r="E41" s="3">
         <v>335000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>304700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>309100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>269800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>242600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>158100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>180500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>142600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>168600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>89400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>71600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>64400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>76900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>52000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>65700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>91700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>105200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>95800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>113800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>121900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>109100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>239100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>226800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>407100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>182000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>161300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>257900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>112500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>93900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>72900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>66500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>44200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>32000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>26100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>41600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>270200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>46200</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>77300</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4366,263 +4456,272 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>365000</v>
+      </c>
+      <c r="E43" s="3">
         <v>379800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>367500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>388100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>374700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>383100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>422800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>415500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>417200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>433700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>480000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>507300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>502300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>479300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>494700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>447900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>367100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>320100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>301200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>291700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>264000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>240200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>207800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>210700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>214000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>193400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>177500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>176200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>170700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>168300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>153900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>143800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>141600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>123000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>121500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>113700</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>96600</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>96900</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>85700</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>361700</v>
+      </c>
+      <c r="E44" s="3">
         <v>349600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>340200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>332900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>352700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>344400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>351100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>335300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>343000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>354200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>362900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>337200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>342800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>312000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>287600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>270300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>259600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>251300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>234400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>221600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>226800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>218400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>206000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>178100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>161900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>153600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>148500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>137100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>131700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>126400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>121200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>108600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>117100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>105900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>93300</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>81100</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>72100</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>70100</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E45" s="3">
         <v>33700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>33900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3000</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>24</v>
@@ -4630,220 +4729,226 @@
       <c r="J45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="3">
         <v>28000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5800</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P45" s="3">
         <v>3600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>28600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>44500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>31400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>36700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>32200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>30300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>15900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>14200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>78000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>23700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>19100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>12400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>16100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>15800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>10900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>10300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>10700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>16300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>12800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>10300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>8000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>11200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>9800</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>9400</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>11700</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1116700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1132200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1084600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1058200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1019500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>990700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>954300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>953800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>951500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>983800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>954700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>937000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>937900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>896900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>878800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>815300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>755000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>708800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>661700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>643100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>626900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>645700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>676700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>634800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>795400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>545100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>503000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>582200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>425200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>399300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>364200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>331700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>313200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>268900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>252000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>246200</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>448400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>224800</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>232000</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4868,24 +4973,24 @@
       <c r="J47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="3">
         <v>3600</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O47" s="3">
         <v>3500</v>
       </c>
-      <c r="O47" s="3" t="s">
+      <c r="P47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -4961,109 +5066,112 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>152700</v>
+      </c>
+      <c r="E48" s="3">
         <v>154000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>156500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>153700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>162100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>168000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>163400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>171200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>177200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>180000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>178100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>182600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>183400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>181700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>189700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>193600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>194700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>199400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>196500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>194900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>194100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>204500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>156700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>148400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>139800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>122500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>117300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>60000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>55900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>53100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>50800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>51000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>51300</v>
-      </c>
-      <c r="AJ48" s="3">
-        <v>51600</v>
       </c>
       <c r="AK48" s="3">
         <v>51600</v>
@@ -5072,135 +5180,141 @@
         <v>51600</v>
       </c>
       <c r="AM48" s="3">
+        <v>51600</v>
+      </c>
+      <c r="AN48" s="3">
         <v>47400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>39400</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>31400</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1127800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1131300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1138500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1148700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1154100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1164200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1177400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1188600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1199900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1211400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1223600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1236100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1248700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1261500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1274900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1289400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1303200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1318400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1102500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1112500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1077300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1093600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>815300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>822800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>831400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>839200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>847400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>768300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>724300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>696300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>704200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>675300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>685700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>505500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>510700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>509900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>483700</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>489100</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>456600</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5318,8 +5432,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5437,127 +5554,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E52" s="3">
         <v>8200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>13800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>7900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>7800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>6400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>9800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>8300</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>8000</v>
-      </c>
-      <c r="AM52" s="3">
-        <v>2000</v>
       </c>
       <c r="AN52" s="3">
         <v>2000</v>
       </c>
       <c r="AO52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AP52" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5675,127 +5798,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2481300</v>
+      </c>
+      <c r="E54" s="3">
         <v>2502100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2457600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2434800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2414400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2401500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2369000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2378900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2378200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2436300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2400800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2391400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2383900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2348000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2349000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2304400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2259800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2230800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1965100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1955100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1903300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1949200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1653200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1610700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1771600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1512600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1473900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1417000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1212400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1156600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1127000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1064500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1056900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>835800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>822600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>815700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>981400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>755300</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>722200</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5837,8 +5966,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5880,142 +6010,146 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>104100</v>
+      </c>
+      <c r="E57" s="3">
         <v>106200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>97800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>79100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>73600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>64800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>74700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>81100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>79900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>88100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>95800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>104000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>111200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>87200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>106600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>98700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>90300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>59400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>73400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>48000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>56600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>48200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>63100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>41900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>50100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>36000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>34900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>39000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>35200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>30800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>25700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>21300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>32900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>37600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>42200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>27500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>24300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>26200</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E58" s="3">
         <v>32300</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>11800</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
@@ -6023,23 +6157,23 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>11600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>15000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>14600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>14200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10400</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -6097,8 +6231,8 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-      <c r="AI58" s="3" t="s">
-        <v>24</v>
+      <c r="AI58" s="3">
+        <v>0</v>
       </c>
       <c r="AJ58" s="3" t="s">
         <v>24</v>
@@ -6106,11 +6240,11 @@
       <c r="AK58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AL58" s="3">
-        <v>0</v>
+      <c r="AL58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AM58" s="3">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AN58" s="3">
         <v>10000</v>
@@ -6118,293 +6252,302 @@
       <c r="AO58" s="3">
         <v>10000</v>
       </c>
+      <c r="AP58" s="3">
+        <v>10000</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>164800</v>
+      </c>
+      <c r="E59" s="3">
         <v>144100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>162300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>135400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>149100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>142300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>107100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>88500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>83500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>84700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>65100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>73200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>56900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>113400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>75400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>95300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>92500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>104300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>93900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>102900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>106000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>163700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>83500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>84000</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>71900</v>
       </c>
       <c r="AB59" s="3">
         <v>71900</v>
       </c>
       <c r="AC59" s="3">
+        <v>71900</v>
+      </c>
+      <c r="AD59" s="3">
         <v>59100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>59000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>58600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>62400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>57000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>50400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>46500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>36600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>33100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>45400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>39000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>32300</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>350500</v>
+      </c>
+      <c r="E60" s="3">
         <v>383000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>322200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>300400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>296600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>273500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>232800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>234400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>207600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>225700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>205300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>233300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>220200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>200600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>182000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>193900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>182800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>163700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>167300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>150800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>162700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>211900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>146600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>125900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>122000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>107900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>94100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>98000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>93800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>93200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>82800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>71700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>79300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>74300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>75300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>72800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>73400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>68500</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>56200</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>642400</v>
+      </c>
+      <c r="E61" s="3">
         <v>646900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>649900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>649600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>652200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>652900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>660900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>656500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>685600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>693500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>642200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>578300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>582800</v>
-      </c>
-      <c r="P61" s="3">
-        <v>511500</v>
       </c>
       <c r="Q61" s="3">
         <v>511500</v>
       </c>
       <c r="R61" s="3">
-        <v>451500</v>
+        <v>511500</v>
       </c>
       <c r="S61" s="3">
         <v>451500</v>
@@ -6413,29 +6556,29 @@
         <v>451500</v>
       </c>
       <c r="U61" s="3">
-        <v>200000</v>
+        <v>451500</v>
       </c>
       <c r="V61" s="3">
         <v>200000</v>
       </c>
       <c r="W61" s="3">
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="X61" s="3">
         <v>160000</v>
       </c>
       <c r="Y61" s="3">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>200000</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -6443,22 +6586,22 @@
         <v>0</v>
       </c>
       <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>276500</v>
-      </c>
-      <c r="AF61" s="3">
-        <v>240000</v>
       </c>
       <c r="AG61" s="3">
         <v>240000</v>
       </c>
       <c r="AH61" s="3">
-        <v>195000</v>
+        <v>240000</v>
       </c>
       <c r="AI61" s="3">
         <v>195000</v>
       </c>
       <c r="AJ61" s="3">
-        <v>0</v>
+        <v>195000</v>
       </c>
       <c r="AK61" s="3">
         <v>0</v>
@@ -6467,135 +6610,141 @@
         <v>0</v>
       </c>
       <c r="AM61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN61" s="3">
         <v>176100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>180700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>180200</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E62" s="3">
         <v>6300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7900</v>
-      </c>
-      <c r="N62" s="3">
-        <v>8400</v>
       </c>
       <c r="O62" s="3">
         <v>8400</v>
       </c>
       <c r="P62" s="3">
+        <v>8400</v>
+      </c>
+      <c r="Q62" s="3">
         <v>91800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>116600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>121800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>125100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>128500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>118300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>120200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>126700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>146700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>98700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>100000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>100200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>87700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>84500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>34200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>29700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>27400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>27600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>25900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>26800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>12300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>13000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>17500</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>20500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>21300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6713,8 +6862,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6832,8 +6984,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6951,127 +7106,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1003600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1042100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>982600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>961300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>963300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>941200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>909100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>906100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>905400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>931800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>860000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>824700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>823000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>803900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>810100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>767200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>759400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>743700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>485600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>471000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>449300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>518500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>245300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>225900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>422200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>195600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>178600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>132200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>400000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>360600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>350400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>292600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>301200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>86600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>88300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>90300</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>270000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>270600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>247600</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7113,8 +7274,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7232,8 +7394,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7351,8 +7516,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7470,8 +7638,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7589,127 +7760,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>151400</v>
+      </c>
+      <c r="E72" s="3">
         <v>154300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>169400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>181900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>165500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>184700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>202300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>219800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>230600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>275200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>320700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>357400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>365700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>360500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>371400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>385800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>368900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>364700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>367400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>374500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>356600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>340900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>328300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>312500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>285200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>261700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>246000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>226700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>213900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>199800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>187400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>180000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>169900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>166200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>157000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>139100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>130300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>123200</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>118000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7827,8 +8004,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7946,8 +8126,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8065,127 +8248,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1477700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1460000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1475000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1473500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1451100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1460300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1459800</v>
-      </c>
-      <c r="J76" s="3">
-        <v>1472800</v>
       </c>
       <c r="K76" s="3">
         <v>1472800</v>
       </c>
       <c r="L76" s="3">
+        <v>1472800</v>
+      </c>
+      <c r="M76" s="3">
         <v>1504500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1540800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1566700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1560900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1544100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1538900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1537200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1500400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1487100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1479500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1484100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1454000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1430600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1407900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1384800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1349400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1317100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1295300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1284700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>812400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>796100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>776600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>771900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>755800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>749200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>734300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>725400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>711400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>484700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>474500</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8303,251 +8492,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46108</v>
+      </c>
+      <c r="E80" s="2">
         <v>46017</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45835</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45744</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45653</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45562</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45471</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45380</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45289</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45198</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44925</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44743</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44652</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44470</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44379</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44288</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44197</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44106</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44015</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43917</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43826</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43735</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-15100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>16400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-19200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-17600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-17500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-44600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-45600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-36700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-14300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>16900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>17900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>15600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>12700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>15800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>27200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>23600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>15700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>19200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>12800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>14100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>12400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>7500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>10100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>9100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>18000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>8800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>7000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>5200</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8589,127 +8787,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E83" s="3">
         <v>9800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>10000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>10100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>10200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>10100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>11100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>13700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>9100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>27200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>23700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>23400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>24500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>24100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>21500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>20800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>20000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>13300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>13000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>12700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>12500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>11400</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>11600</v>
       </c>
       <c r="AE83" s="3">
         <v>11600</v>
       </c>
       <c r="AF83" s="3">
+        <v>11600</v>
+      </c>
+      <c r="AG83" s="3">
         <v>11700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>11500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>12000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>11400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>9600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>9300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>9100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>8000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>7900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8827,8 +9029,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8946,8 +9151,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9065,8 +9273,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9184,8 +9395,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9303,127 +9517,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E89" s="3">
         <v>51600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>38100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>30000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>85500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-14700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>71800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-17800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>45500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-39100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>12600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>35400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-66000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-19400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>6800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>27200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>23200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>23900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>22900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>28700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>30100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>32100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>24300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>26000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>26200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>25300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>20000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>25600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>8800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>8000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>9700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>24900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>14200</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9465,127 +9685,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7900</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-8000</v>
       </c>
       <c r="M91" s="3">
         <v>-8000</v>
       </c>
       <c r="N91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="O91" s="3">
         <v>-8800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-6100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-8000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-10900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-10000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-13800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-10900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-11300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-8800</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-7100</v>
       </c>
       <c r="AF91" s="3">
         <v>-7100</v>
       </c>
       <c r="AG91" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9703,8 +9927,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9822,127 +10049,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7900</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-8000</v>
       </c>
       <c r="M94" s="3">
         <v>-8000</v>
       </c>
       <c r="N94" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="O94" s="3">
         <v>-8800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-8400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-251300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-8600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-78500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-71600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-255900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-11500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-11300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-106100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-54400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-43600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-183100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-3800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-10000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-46900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-11600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-46500</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-6200</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9984,8 +10217,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10025,8 +10259,8 @@
       <c r="O96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10103,8 +10337,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10222,8 +10459,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10341,8 +10581,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10460,159 +10703,165 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-15400</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="F100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2200</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>1500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-23500</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>41200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>65000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3100</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>2400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>59900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>253800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-7300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>43100</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>163200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-197600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>201600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-14600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>173900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>36000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>36300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>194800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-192100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>210800</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>1200</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-8500</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>700</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-300</v>
       </c>
       <c r="N101" s="3">
         <v>-300</v>
@@ -10621,10 +10870,10 @@
         <v>-300</v>
       </c>
       <c r="P101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q101" s="3">
         <v>300</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-300</v>
       </c>
       <c r="R101" s="3">
         <v>-300</v>
@@ -10633,38 +10882,38 @@
         <v>-300</v>
       </c>
       <c r="T101" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-400</v>
-      </c>
-      <c r="X101" s="3">
-        <v>400</v>
       </c>
       <c r="Y101" s="3">
         <v>400</v>
       </c>
       <c r="Z101" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-300</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
         <v>0</v>
       </c>
@@ -10675,146 +10924,152 @@
         <v>0</v>
       </c>
       <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>300</v>
       </c>
-      <c r="AK101" s="3">
-        <v>0</v>
-      </c>
       <c r="AL101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="3">
         <v>700</v>
-      </c>
-      <c r="AM101" s="3">
-        <v>-100</v>
       </c>
       <c r="AN101" s="3">
         <v>-100</v>
       </c>
       <c r="AO101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AP101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E102" s="3">
         <v>30300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>39300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>27300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>84400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-22400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>37900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-26000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>79300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>17800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-12500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>25000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-13700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-26000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-13500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>9400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-18000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-8100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-48800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-68400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>12300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-180300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>225100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>20700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-96600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>145400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>18600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>21000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>6300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>22300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>12200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>6000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-15600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-228600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>224100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-31100</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-4400</v>
       </c>
     </row>
